--- a/2026/EL MIRADOR/Septiembre/Septiembre - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Septiembre/Septiembre - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883CCD8D-D75F-4D88-8DE5-226F0E7531DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1DD4D2-84F3-4F72-987C-B3CA9ABE1389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,16 +26,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="432">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1167,24 +1162,6 @@
     <t>TOTAL DEUDA</t>
   </si>
   <si>
-    <t>Local 2</t>
-  </si>
-  <si>
-    <t>Pago $34.752 y $770.504 de expensas y arba</t>
-  </si>
-  <si>
-    <t>El 5C pago con cualquier centavo, abono $529.029,96 el 07/09</t>
-  </si>
-  <si>
-    <t>5C</t>
-  </si>
-  <si>
-    <t>Jose ferraro</t>
-  </si>
-  <si>
-    <t>Jose Ferraro deposito $526.500 el 14/09</t>
-  </si>
-  <si>
     <t>Transf 16/09</t>
   </si>
   <si>
@@ -1336,6 +1313,27 @@
   </si>
   <si>
     <t>TSG:</t>
+  </si>
+  <si>
+    <t>Cochera 32</t>
+  </si>
+  <si>
+    <t>A la cochera 32 no le debemos cobrar el TSG, debe abonar:  $42.523,01</t>
+  </si>
+  <si>
+    <t>13C</t>
+  </si>
+  <si>
+    <t>Javier Argentino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13C transfirio $319.842 el 09/10 </t>
+  </si>
+  <si>
+    <t>Cocher 35</t>
+  </si>
+  <si>
+    <t>Cochera 35 transfirio el 09/10 $42.523</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1673,6 +1671,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2026,7 +2030,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="412">
+  <cellXfs count="413">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2342,11 +2346,6 @@
     <xf numFmtId="10" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2382,18 +2381,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2405,16 +2395,15 @@
     <xf numFmtId="44" fontId="10" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="19" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2515,6 +2504,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2676,6 +2674,18 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="23" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2707,19 +2717,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2748,13 +2746,18 @@
     <xf numFmtId="0" fontId="18" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="19" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2836,9 +2839,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2876,9 +2879,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2911,26 +2914,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2963,26 +2949,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3157,24 +3126,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N139"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="68"/>
       <c r="B1" s="76"/>
       <c r="C1" s="81" t="s">
@@ -3188,7 +3157,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="67"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="69"/>
       <c r="B2" s="77"/>
       <c r="C2" s="77" t="s">
@@ -3202,7 +3171,7 @@
       <c r="I2" s="78"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="69"/>
       <c r="B3" s="77"/>
       <c r="C3" s="77" t="s">
@@ -3218,7 +3187,7 @@
       <c r="I3" s="78"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="69"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77" t="s">
@@ -3232,11 +3201,11 @@
       <c r="I4" s="78"/>
       <c r="J4" s="65"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="72"/>
       <c r="B5" s="77"/>
       <c r="C5" s="77" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D5" s="77"/>
       <c r="E5" s="77" t="s">
@@ -3248,7 +3217,7 @@
       <c r="I5" s="77"/>
       <c r="J5" s="73"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="72"/>
       <c r="B6" s="77"/>
       <c r="C6" s="77" t="s">
@@ -3262,7 +3231,7 @@
       <c r="I6" s="77"/>
       <c r="J6" s="73"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -3274,115 +3243,115 @@
       <c r="I7" s="75"/>
       <c r="J7" s="79"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="331" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="325" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="331"/>
-      <c r="C14" s="331"/>
-      <c r="D14" s="331"/>
-      <c r="E14" s="331"/>
-      <c r="F14" s="331"/>
-      <c r="G14" s="331"/>
-      <c r="H14" s="331"/>
-      <c r="I14" s="331"/>
-      <c r="J14" s="331"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="331"/>
-      <c r="B15" s="331"/>
-      <c r="C15" s="331"/>
-      <c r="D15" s="331"/>
-      <c r="E15" s="331"/>
-      <c r="F15" s="331"/>
-      <c r="G15" s="331"/>
-      <c r="H15" s="331"/>
-      <c r="I15" s="331"/>
-      <c r="J15" s="331"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="331"/>
-      <c r="B16" s="331"/>
-      <c r="C16" s="331"/>
-      <c r="D16" s="331"/>
-      <c r="E16" s="331"/>
-      <c r="F16" s="331"/>
-      <c r="G16" s="331"/>
-      <c r="H16" s="331"/>
-      <c r="I16" s="331"/>
-      <c r="J16" s="331"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="331"/>
-      <c r="B17" s="331"/>
-      <c r="C17" s="331"/>
-      <c r="D17" s="331"/>
-      <c r="E17" s="331"/>
-      <c r="F17" s="331"/>
-      <c r="G17" s="331"/>
-      <c r="H17" s="331"/>
-      <c r="I17" s="331"/>
-      <c r="J17" s="331"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="331"/>
-      <c r="B18" s="331"/>
-      <c r="C18" s="331"/>
-      <c r="D18" s="331"/>
-      <c r="E18" s="331"/>
-      <c r="F18" s="331"/>
-      <c r="G18" s="331"/>
-      <c r="H18" s="331"/>
-      <c r="I18" s="331"/>
-      <c r="J18" s="331"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="325"/>
+      <c r="C14" s="325"/>
+      <c r="D14" s="325"/>
+      <c r="E14" s="325"/>
+      <c r="F14" s="325"/>
+      <c r="G14" s="325"/>
+      <c r="H14" s="325"/>
+      <c r="I14" s="325"/>
+      <c r="J14" s="325"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="325"/>
+      <c r="B15" s="325"/>
+      <c r="C15" s="325"/>
+      <c r="D15" s="325"/>
+      <c r="E15" s="325"/>
+      <c r="F15" s="325"/>
+      <c r="G15" s="325"/>
+      <c r="H15" s="325"/>
+      <c r="I15" s="325"/>
+      <c r="J15" s="325"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="325"/>
+      <c r="B16" s="325"/>
+      <c r="C16" s="325"/>
+      <c r="D16" s="325"/>
+      <c r="E16" s="325"/>
+      <c r="F16" s="325"/>
+      <c r="G16" s="325"/>
+      <c r="H16" s="325"/>
+      <c r="I16" s="325"/>
+      <c r="J16" s="325"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="325"/>
+      <c r="B17" s="325"/>
+      <c r="C17" s="325"/>
+      <c r="D17" s="325"/>
+      <c r="E17" s="325"/>
+      <c r="F17" s="325"/>
+      <c r="G17" s="325"/>
+      <c r="H17" s="325"/>
+      <c r="I17" s="325"/>
+      <c r="J17" s="325"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="325"/>
+      <c r="B18" s="325"/>
+      <c r="C18" s="325"/>
+      <c r="D18" s="325"/>
+      <c r="E18" s="325"/>
+      <c r="F18" s="325"/>
+      <c r="G18" s="325"/>
+      <c r="H18" s="325"/>
+      <c r="I18" s="325"/>
+      <c r="J18" s="325"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="332" t="s">
-        <v>381</v>
-      </c>
-      <c r="B20" s="332"/>
-      <c r="C20" s="332"/>
-      <c r="D20" s="332"/>
-      <c r="E20" s="332"/>
-      <c r="F20" s="332"/>
-      <c r="G20" s="332"/>
-      <c r="H20" s="332"/>
-      <c r="I20" s="332"/>
-      <c r="J20" s="332"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="332"/>
-      <c r="B21" s="332"/>
-      <c r="C21" s="332"/>
-      <c r="D21" s="332"/>
-      <c r="E21" s="332"/>
-      <c r="F21" s="332"/>
-      <c r="G21" s="332"/>
-      <c r="H21" s="332"/>
-      <c r="I21" s="332"/>
-      <c r="J21" s="332"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="332"/>
-      <c r="B22" s="332"/>
-      <c r="C22" s="332"/>
-      <c r="D22" s="332"/>
-      <c r="E22" s="332"/>
-      <c r="F22" s="332"/>
-      <c r="G22" s="332"/>
-      <c r="H22" s="332"/>
-      <c r="I22" s="332"/>
-      <c r="J22" s="332"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="326" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20" s="326"/>
+      <c r="C20" s="326"/>
+      <c r="D20" s="326"/>
+      <c r="E20" s="326"/>
+      <c r="F20" s="326"/>
+      <c r="G20" s="326"/>
+      <c r="H20" s="326"/>
+      <c r="I20" s="326"/>
+      <c r="J20" s="326"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="326"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="326"/>
+      <c r="D21" s="326"/>
+      <c r="E21" s="326"/>
+      <c r="F21" s="326"/>
+      <c r="G21" s="326"/>
+      <c r="H21" s="326"/>
+      <c r="I21" s="326"/>
+      <c r="J21" s="326"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="326"/>
+      <c r="B22" s="326"/>
+      <c r="C22" s="326"/>
+      <c r="D22" s="326"/>
+      <c r="E22" s="326"/>
+      <c r="F22" s="326"/>
+      <c r="G22" s="326"/>
+      <c r="H22" s="326"/>
+      <c r="I22" s="326"/>
+      <c r="J22" s="326"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
@@ -3390,11 +3359,11 @@
       <c r="E23" s="56"/>
       <c r="F23" s="56"/>
       <c r="G23" s="56"/>
-      <c r="H23" s="251"/>
+      <c r="H23" s="246"/>
       <c r="I23" s="56"/>
       <c r="J23" s="56"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="180" t="s">
         <v>17</v>
       </c>
@@ -3416,11 +3385,11 @@
       <c r="I24" s="184" t="s">
         <v>167</v>
       </c>
-      <c r="J24" s="252" t="s">
+      <c r="J24" s="247" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="185" t="s">
         <v>328</v>
       </c>
@@ -3435,15 +3404,15 @@
       <c r="J25" s="186"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="187" t="s">
         <v>351</v>
       </c>
       <c r="B26" s="157" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C26" s="235" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D26" s="155">
         <v>2966292</v>
@@ -3456,13 +3425,13 @@
       <c r="J26" s="157"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="187" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B27" s="157"/>
       <c r="C27" s="235" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D27" s="155">
         <v>120000</v>
@@ -3475,7 +3444,7 @@
       <c r="J27" s="157"/>
       <c r="L27" s="43"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="188" t="s">
         <v>34</v>
       </c>
@@ -3518,7 +3487,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="187" t="s">
         <v>229</v>
       </c>
@@ -3533,7 +3502,7 @@
       <c r="J29" s="186"/>
       <c r="L29" s="43"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="187"/>
       <c r="B30" s="157"/>
       <c r="C30" s="157"/>
@@ -3546,7 +3515,7 @@
       <c r="J30" s="186"/>
       <c r="L30" s="43"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="188" t="s">
         <v>15</v>
       </c>
@@ -3564,7 +3533,7 @@
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
-      <c r="J31" s="253"/>
+      <c r="J31" s="248"/>
       <c r="K31" s="31">
         <f>E31+J31+F31+G31+H31+I31</f>
         <v>0</v>
@@ -3574,7 +3543,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="187" t="s">
         <v>225</v>
       </c>
@@ -3589,15 +3558,15 @@
       <c r="J32" s="190"/>
       <c r="L32" s="43"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="119" t="s">
         <v>344</v>
       </c>
       <c r="B33" s="119" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C33" s="220" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D33" s="155">
         <v>1916441</v>
@@ -3610,15 +3579,15 @@
       <c r="J33" s="190"/>
       <c r="L33" s="43"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="119" t="s">
         <v>228</v>
       </c>
       <c r="B34" s="119" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C34" s="220" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D34" s="155">
         <v>1916441</v>
@@ -3631,15 +3600,15 @@
       <c r="J34" s="190"/>
       <c r="L34" s="43"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="119" t="s">
         <v>344</v>
       </c>
       <c r="B35" s="119" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C35" s="220" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D35" s="155">
         <f>3791724/2</f>
@@ -3653,15 +3622,15 @@
       <c r="J35" s="190"/>
       <c r="L35" s="43"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="119" t="s">
         <v>228</v>
       </c>
       <c r="B36" s="119" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C36" s="220" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D36" s="155">
         <f>3791724/2</f>
@@ -3675,7 +3644,7 @@
       <c r="J36" s="190"/>
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="119"/>
       <c r="B37" s="119"/>
       <c r="C37" s="119"/>
@@ -3688,7 +3657,7 @@
       <c r="J37" s="190"/>
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="188" t="s">
         <v>227</v>
       </c>
@@ -3731,7 +3700,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="187" t="s">
         <v>1</v>
       </c>
@@ -3746,7 +3715,7 @@
       <c r="J39" s="157"/>
       <c r="L39" s="43"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="157"/>
       <c r="B40" s="157"/>
       <c r="C40" s="157"/>
@@ -3759,7 +3728,7 @@
       <c r="J40" s="157"/>
       <c r="L40" s="43"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="188" t="s">
         <v>226</v>
       </c>
@@ -3802,7 +3771,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="187" t="s">
         <v>218</v>
       </c>
@@ -3814,10 +3783,10 @@
       <c r="G42" s="194"/>
       <c r="H42" s="194"/>
       <c r="I42" s="194"/>
-      <c r="J42" s="254"/>
+      <c r="J42" s="249"/>
       <c r="L42" s="43"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="157" t="s">
         <v>222</v>
       </c>
@@ -3858,9 +3827,9 @@
       </c>
       <c r="L43" s="43"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="333"/>
-      <c r="B44" s="334"/>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="327"/>
+      <c r="B44" s="328"/>
       <c r="C44" s="157"/>
       <c r="D44" s="32"/>
       <c r="E44" s="186"/>
@@ -3872,7 +3841,7 @@
       <c r="K44" s="31"/>
       <c r="L44" s="43"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="188" t="s">
         <v>2</v>
       </c>
@@ -3915,7 +3884,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="187" t="s">
         <v>3</v>
       </c>
@@ -3930,15 +3899,15 @@
       <c r="J46" s="157"/>
       <c r="L46" s="43"/>
     </row>
-    <row r="47" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="196" t="s">
         <v>360</v>
       </c>
       <c r="B47" s="157"/>
       <c r="C47" s="235" t="s">
-        <v>380</v>
-      </c>
-      <c r="D47" s="411">
+        <v>374</v>
+      </c>
+      <c r="D47" s="284">
         <v>2645102.88</v>
       </c>
       <c r="E47" s="197">
@@ -3976,15 +3945,15 @@
       <c r="M47" s="55"/>
       <c r="N47" s="55"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="157" t="s">
         <v>223</v>
       </c>
       <c r="B48" s="157"/>
       <c r="C48" s="235" t="s">
-        <v>410</v>
-      </c>
-      <c r="D48" s="411">
+        <v>404</v>
+      </c>
+      <c r="D48" s="284">
         <v>7010415.0899999999</v>
       </c>
       <c r="E48" s="197">
@@ -4022,13 +3991,13 @@
       <c r="M48" s="55"/>
       <c r="N48" s="55"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="157" t="s">
         <v>224</v>
       </c>
       <c r="B49" s="157"/>
       <c r="C49" s="157" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D49" s="32">
         <v>176275.21</v>
@@ -4059,13 +4028,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="196" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B50" s="157"/>
       <c r="C50" s="220" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D50" s="32">
         <v>427893</v>
@@ -4090,13 +4059,13 @@
       <c r="M50" s="55"/>
       <c r="N50" s="55"/>
     </row>
-    <row r="51" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="293" t="s">
-        <v>385</v>
-      </c>
-      <c r="B51" s="330"/>
+    <row r="51" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="321" t="s">
+        <v>379</v>
+      </c>
+      <c r="B51" s="324"/>
       <c r="C51" s="235" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D51" s="32">
         <v>55000</v>
@@ -4127,13 +4096,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="119" t="s">
         <v>253</v>
       </c>
       <c r="B52" s="218"/>
       <c r="C52" s="235" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D52" s="32">
         <v>8144.29</v>
@@ -4158,13 +4127,13 @@
       <c r="M52" s="55"/>
       <c r="N52" s="55"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="119" t="s">
         <v>254</v>
       </c>
       <c r="B53" s="119"/>
       <c r="C53" s="235" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D53" s="32">
         <v>1751133.84</v>
@@ -4210,13 +4179,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="198" t="s">
         <v>252</v>
       </c>
       <c r="B54" s="199"/>
       <c r="C54" s="235" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D54" s="32">
         <v>120000</v>
@@ -4247,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="188" t="s">
         <v>4</v>
       </c>
@@ -4294,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="157"/>
       <c r="B56" s="157"/>
       <c r="C56" s="157"/>
@@ -4307,7 +4276,7 @@
       <c r="J56" s="157"/>
       <c r="L56" s="43"/>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="157"/>
       <c r="B57" s="157"/>
       <c r="C57" s="157"/>
@@ -4320,7 +4289,7 @@
       <c r="J57" s="157"/>
       <c r="L57" s="43"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="187" t="s">
         <v>219</v>
       </c>
@@ -4335,13 +4304,13 @@
       <c r="J58" s="157"/>
       <c r="L58" s="43"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="191" t="s">
         <v>327</v>
       </c>
       <c r="B59" s="200"/>
       <c r="C59" s="235" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D59" s="32">
         <v>230000</v>
@@ -4364,13 +4333,13 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="293" t="s">
-        <v>389</v>
-      </c>
-      <c r="B60" s="330"/>
+    <row r="60" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="321" t="s">
+        <v>383</v>
+      </c>
+      <c r="B60" s="324"/>
       <c r="C60" s="119" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D60" s="32">
         <v>130000</v>
@@ -4408,13 +4377,13 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="293" t="s">
-        <v>420</v>
-      </c>
-      <c r="B61" s="330"/>
+    <row r="61" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="321" t="s">
+        <v>414</v>
+      </c>
+      <c r="B61" s="324"/>
       <c r="C61" s="235" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D61" s="32">
         <v>1379400</v>
@@ -4452,13 +4421,13 @@
         <v>1379400.0000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="407" t="s">
-        <v>423</v>
-      </c>
-      <c r="B62" s="278"/>
+    <row r="62" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="280" t="s">
+        <v>417</v>
+      </c>
+      <c r="B62" s="218"/>
       <c r="C62" s="235" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D62" s="32">
         <v>516621.6</v>
@@ -4496,13 +4465,13 @@
         <v>516621.60000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="407" t="s">
-        <v>423</v>
-      </c>
-      <c r="B63" s="243"/>
+    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="280" t="s">
+        <v>417</v>
+      </c>
+      <c r="B63" s="238"/>
       <c r="C63" s="235" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D63" s="32">
         <v>373188.2</v>
@@ -4540,38 +4509,38 @@
         <v>373188.19999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="188" t="s">
         <v>220</v>
       </c>
       <c r="B64" s="188"/>
       <c r="C64" s="188"/>
       <c r="D64" s="30">
-        <f>SUM(D59:D63)</f>
+        <f t="shared" ref="D64:J64" si="18">SUM(D59:D63)</f>
         <v>2629209.8000000003</v>
       </c>
       <c r="E64" s="30">
-        <f>SUM(E59:E63)</f>
+        <f t="shared" si="18"/>
         <v>2466063.5336000002</v>
       </c>
       <c r="F64" s="30">
-        <f>SUM(F59:F63)</f>
+        <f t="shared" si="18"/>
         <v>25911.465840000001</v>
       </c>
       <c r="G64" s="30">
-        <f>SUM(G59:G63)</f>
+        <f t="shared" si="18"/>
         <v>30709.885439999998</v>
       </c>
       <c r="H64" s="30">
-        <f>SUM(H59:H63)</f>
+        <f t="shared" si="18"/>
         <v>29030.438579999995</v>
       </c>
       <c r="I64" s="30">
-        <f>SUM(I59:I63)</f>
+        <f t="shared" si="18"/>
         <v>35748.226020000002</v>
       </c>
       <c r="J64" s="30">
-        <f>SUM(J59:J63)</f>
+        <f t="shared" si="18"/>
         <v>41746.250519999994</v>
       </c>
       <c r="K64" s="31">
@@ -4585,7 +4554,7 @@
       <c r="M64" s="31"/>
       <c r="N64" s="31"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="187" t="s">
         <v>5</v>
       </c>
@@ -4600,13 +4569,13 @@
       <c r="J65" s="157"/>
       <c r="L65" s="43"/>
     </row>
-    <row r="66" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="328" t="s">
-        <v>407</v>
-      </c>
-      <c r="B66" s="329"/>
+    <row r="66" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="319" t="s">
+        <v>401</v>
+      </c>
+      <c r="B66" s="320"/>
       <c r="C66" s="157" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D66" s="32">
         <v>949849</v>
@@ -4640,13 +4609,13 @@
         <v>361</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="328" t="s">
-        <v>424</v>
-      </c>
-      <c r="B67" s="329"/>
+    <row r="67" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="319" t="s">
+        <v>418</v>
+      </c>
+      <c r="B67" s="320"/>
       <c r="C67" s="235" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D67" s="32">
         <v>103000</v>
@@ -4678,7 +4647,7 @@
       <c r="L67" s="43"/>
       <c r="N67" s="32"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="157"/>
       <c r="B68" s="157"/>
       <c r="C68" s="157"/>
@@ -4692,7 +4661,7 @@
       <c r="L68" s="43"/>
       <c r="N68" s="31"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="188" t="s">
         <v>6</v>
       </c>
@@ -4707,19 +4676,19 @@
         <v>981255.26800000004</v>
       </c>
       <c r="F69" s="30">
-        <f t="shared" ref="F69:I69" si="18">SUM(F66:F68)</f>
+        <f t="shared" ref="F69:I69" si="19">SUM(F66:F68)</f>
         <v>11370.769200000001</v>
       </c>
       <c r="G69" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13476.467200000001</v>
       </c>
       <c r="H69" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12739.472899999999</v>
       </c>
       <c r="I69" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15687.4501</v>
       </c>
       <c r="J69" s="30">
@@ -4736,7 +4705,7 @@
       </c>
       <c r="N69" s="31"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="157" t="s">
         <v>25</v>
       </c>
@@ -4771,7 +4740,7 @@
       </c>
       <c r="L70" s="43"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="157" t="s">
         <v>26</v>
       </c>
@@ -4806,7 +4775,7 @@
       </c>
       <c r="L71" s="43"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="188" t="s">
         <v>221</v>
       </c>
@@ -4817,27 +4786,27 @@
         <v>690677.73</v>
       </c>
       <c r="E72" s="45">
-        <f t="shared" ref="E72:J72" si="19">SUM(E70:E71)</f>
+        <f t="shared" ref="E72:J72" si="20">SUM(E70:E71)</f>
         <v>643711.64436000003</v>
       </c>
       <c r="F72" s="45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7459.3194839999996</v>
       </c>
       <c r="G72" s="45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8840.6749440000003</v>
       </c>
       <c r="H72" s="45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8357.2005329999993</v>
       </c>
       <c r="I72" s="45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10291.098177</v>
       </c>
       <c r="J72" s="45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12017.792501999998</v>
       </c>
       <c r="K72" s="31">
@@ -4849,7 +4818,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="61"/>
       <c r="B73" s="61"/>
       <c r="C73" s="61"/>
@@ -4862,12 +4831,12 @@
       <c r="J73" s="61"/>
       <c r="L73" s="43"/>
     </row>
-    <row r="74" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="325" t="s">
-        <v>429</v>
-      </c>
-      <c r="B74" s="326"/>
-      <c r="C74" s="327"/>
+    <row r="74" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="316" t="s">
+        <v>423</v>
+      </c>
+      <c r="B74" s="317"/>
+      <c r="C74" s="318"/>
       <c r="D74" s="62">
         <f>-D61</f>
         <v>-1379400</v>
@@ -4892,7 +4861,7 @@
         <f>$D74*1.49%</f>
         <v>-20553.060000000001</v>
       </c>
-      <c r="J74" s="255">
+      <c r="J74" s="250">
         <f>D74*1.74%</f>
         <v>-24001.559999999998</v>
       </c>
@@ -4905,7 +4874,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="205"/>
       <c r="B75" s="206"/>
       <c r="C75" s="206"/>
@@ -4915,42 +4884,42 @@
       <c r="G75" s="63"/>
       <c r="H75" s="63"/>
       <c r="I75" s="63"/>
-      <c r="J75" s="256"/>
+      <c r="J75" s="251"/>
       <c r="K75" s="31"/>
       <c r="L75" s="43"/>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="207" t="s">
         <v>27</v>
       </c>
       <c r="B76" s="208"/>
       <c r="C76" s="209"/>
       <c r="D76" s="57">
-        <f t="shared" ref="D76:J76" si="20">SUM(D74+D38+D31+D72+D69+D64+D55+D45+D28++D41)</f>
+        <f t="shared" ref="D76:J76" si="21">SUM(D74+D38+D31+D72+D69+D64+D55+D45+D28++D41)</f>
         <v>26112569.84</v>
       </c>
       <c r="E76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24406092.340879999</v>
       </c>
       <c r="F76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>271028.77927200001</v>
       </c>
       <c r="G76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>321219.29395200004</v>
       </c>
       <c r="H76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>303652.61381399992</v>
       </c>
       <c r="I76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>373919.33436599997</v>
       </c>
       <c r="J76" s="57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>436657.47771599999</v>
       </c>
       <c r="K76" s="41">
@@ -4966,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="56"/>
       <c r="B77" s="56"/>
       <c r="C77" s="56"/>
@@ -4978,7 +4947,7 @@
       <c r="I77" s="210"/>
       <c r="J77" s="56"/>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="211" t="s">
         <v>35</v>
       </c>
@@ -4992,10 +4961,10 @@
       <c r="I78" s="210"/>
       <c r="J78" s="56"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="213"/>
       <c r="B79" s="56"/>
-      <c r="C79" s="257"/>
+      <c r="C79" s="252"/>
       <c r="D79" s="56"/>
       <c r="E79" s="210"/>
       <c r="F79" s="210"/>
@@ -5004,10 +4973,10 @@
       <c r="I79" s="210"/>
       <c r="J79" s="56"/>
     </row>
-    <row r="80" spans="1:14" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="213"/>
       <c r="B80" s="56"/>
-      <c r="C80" s="257"/>
+      <c r="C80" s="252"/>
       <c r="D80" s="210"/>
       <c r="E80" s="210"/>
       <c r="F80" s="210"/>
@@ -5016,7 +4985,7 @@
       <c r="I80" s="210"/>
       <c r="J80" s="56"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="214" t="s">
         <v>15</v>
       </c>
@@ -5033,7 +5002,7 @@
       <c r="I81" s="210"/>
       <c r="J81" s="56"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="56"/>
       <c r="B82" s="56"/>
       <c r="C82" s="56"/>
@@ -5044,7 +5013,7 @@
       <c r="H82" s="31"/>
       <c r="I82" s="31"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="56"/>
       <c r="B83" s="56"/>
       <c r="C83" s="56"/>
@@ -5055,13 +5024,13 @@
       <c r="H83" s="40"/>
       <c r="I83" s="40"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="312" t="s">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="303" t="s">
         <v>31</v>
       </c>
-      <c r="B84" s="313"/>
-      <c r="C84" s="313"/>
-      <c r="D84" s="313"/>
+      <c r="B84" s="304"/>
+      <c r="C84" s="304"/>
+      <c r="D84" s="304"/>
       <c r="E84" s="51" t="s">
         <v>9</v>
       </c>
@@ -5081,9 +5050,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="293"/>
-      <c r="B85" s="294"/>
+    <row r="85" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="321"/>
+      <c r="B85" s="322"/>
       <c r="C85" s="218"/>
       <c r="D85" s="32"/>
       <c r="E85" s="197">
@@ -5096,9 +5065,9 @@
       <c r="I85" s="42"/>
       <c r="J85" s="38"/>
     </row>
-    <row r="86" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="314"/>
-      <c r="B86" s="315"/>
+    <row r="86" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="305"/>
+      <c r="B86" s="306"/>
       <c r="C86" s="53"/>
       <c r="D86" s="32"/>
       <c r="E86" s="42"/>
@@ -5108,12 +5077,12 @@
       <c r="I86" s="42"/>
       <c r="J86" s="38"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="309" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="300" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="310"/>
-      <c r="C87" s="311"/>
+      <c r="B87" s="301"/>
+      <c r="C87" s="302"/>
       <c r="D87" s="50">
         <f>SUM(D85:D86)</f>
         <v>0</v>
@@ -5139,14 +5108,14 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E89" s="31"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
       <c r="I89" s="31"/>
     </row>
-    <row r="90" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="26" t="s">
         <v>28</v>
       </c>
@@ -5155,7 +5124,7 @@
         <v>26112569.84</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="28" t="s">
         <v>30</v>
       </c>
@@ -5163,45 +5132,45 @@
         <f>D76-D74</f>
         <v>27491969.84</v>
       </c>
-      <c r="D91" s="295" t="s">
+      <c r="D91" s="323" t="s">
         <v>362</v>
       </c>
-      <c r="E91" s="295"/>
-      <c r="F91" s="295"/>
-      <c r="G91" s="295"/>
-      <c r="H91" s="295"/>
-      <c r="I91" s="295"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D92" s="295"/>
-      <c r="E92" s="295"/>
-      <c r="F92" s="295"/>
-      <c r="G92" s="295"/>
-      <c r="H92" s="295"/>
-      <c r="I92" s="295"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D93" s="295"/>
-      <c r="E93" s="295"/>
-      <c r="F93" s="295"/>
-      <c r="G93" s="295"/>
-      <c r="H93" s="295"/>
-      <c r="I93" s="295"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E91" s="323"/>
+      <c r="F91" s="323"/>
+      <c r="G91" s="323"/>
+      <c r="H91" s="323"/>
+      <c r="I91" s="323"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D92" s="323"/>
+      <c r="E92" s="323"/>
+      <c r="F92" s="323"/>
+      <c r="G92" s="323"/>
+      <c r="H92" s="323"/>
+      <c r="I92" s="323"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D93" s="323"/>
+      <c r="E93" s="323"/>
+      <c r="F93" s="323"/>
+      <c r="G93" s="323"/>
+      <c r="H93" s="323"/>
+      <c r="I93" s="323"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>364</v>
       </c>
       <c r="B94" s="8"/>
       <c r="C94" s="9"/>
-      <c r="D94" s="295"/>
-      <c r="E94" s="295"/>
-      <c r="F94" s="295"/>
-      <c r="G94" s="295"/>
-      <c r="H94" s="295"/>
-      <c r="I94" s="295"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D94" s="323"/>
+      <c r="E94" s="323"/>
+      <c r="F94" s="323"/>
+      <c r="G94" s="323"/>
+      <c r="H94" s="323"/>
+      <c r="I94" s="323"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>19</v>
       </c>
@@ -5209,14 +5178,14 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C95" s="11"/>
-      <c r="D95" s="295"/>
-      <c r="E95" s="295"/>
-      <c r="F95" s="295"/>
-      <c r="G95" s="295"/>
-      <c r="H95" s="295"/>
-      <c r="I95" s="295"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D95" s="323"/>
+      <c r="E95" s="323"/>
+      <c r="F95" s="323"/>
+      <c r="G95" s="323"/>
+      <c r="H95" s="323"/>
+      <c r="I95" s="323"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>20</v>
       </c>
@@ -5227,14 +5196,14 @@
       <c r="C96" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="295"/>
-      <c r="E96" s="295"/>
-      <c r="F96" s="295"/>
-      <c r="G96" s="295"/>
-      <c r="H96" s="295"/>
-      <c r="I96" s="295"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D96" s="323"/>
+      <c r="E96" s="323"/>
+      <c r="F96" s="323"/>
+      <c r="G96" s="323"/>
+      <c r="H96" s="323"/>
+      <c r="I96" s="323"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>331</v>
       </c>
@@ -5243,14 +5212,14 @@
         <v>34752</v>
       </c>
       <c r="C97" s="11"/>
-      <c r="D97" s="295"/>
-      <c r="E97" s="295"/>
-      <c r="F97" s="295"/>
-      <c r="G97" s="295"/>
-      <c r="H97" s="295"/>
-      <c r="I97" s="295"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D97" s="323"/>
+      <c r="E97" s="323"/>
+      <c r="F97" s="323"/>
+      <c r="G97" s="323"/>
+      <c r="H97" s="323"/>
+      <c r="I97" s="323"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
         <v>33</v>
       </c>
@@ -5259,15 +5228,15 @@
         <v>-27491969.84</v>
       </c>
       <c r="C98" s="9"/>
-      <c r="D98" s="295"/>
-      <c r="E98" s="295"/>
-      <c r="F98" s="295"/>
-      <c r="G98" s="295"/>
-      <c r="H98" s="295"/>
-      <c r="I98" s="295"/>
+      <c r="D98" s="323"/>
+      <c r="E98" s="323"/>
+      <c r="F98" s="323"/>
+      <c r="G98" s="323"/>
+      <c r="H98" s="323"/>
+      <c r="I98" s="323"/>
       <c r="K98" s="32"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>32</v>
       </c>
@@ -5276,31 +5245,31 @@
         <v>0</v>
       </c>
       <c r="C99" s="9"/>
-      <c r="D99" s="295"/>
-      <c r="E99" s="295"/>
-      <c r="F99" s="295"/>
-      <c r="G99" s="295"/>
-      <c r="H99" s="295"/>
-      <c r="I99" s="295"/>
+      <c r="D99" s="323"/>
+      <c r="E99" s="323"/>
+      <c r="F99" s="323"/>
+      <c r="G99" s="323"/>
+      <c r="H99" s="323"/>
+      <c r="I99" s="323"/>
       <c r="K99" s="33"/>
     </row>
-    <row r="100" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="279" t="s">
-        <v>387</v>
+    <row r="100" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="268" t="s">
+        <v>381</v>
       </c>
       <c r="B100" s="54">
         <v>-209759.2</v>
       </c>
       <c r="C100" s="9"/>
-      <c r="D100" s="295"/>
-      <c r="E100" s="295"/>
-      <c r="F100" s="295"/>
-      <c r="G100" s="295"/>
-      <c r="H100" s="295"/>
-      <c r="I100" s="295"/>
+      <c r="D100" s="323"/>
+      <c r="E100" s="323"/>
+      <c r="F100" s="323"/>
+      <c r="G100" s="323"/>
+      <c r="H100" s="323"/>
+      <c r="I100" s="323"/>
       <c r="K100" s="33"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>266</v>
       </c>
@@ -5309,15 +5278,15 @@
         <v>0</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="295"/>
-      <c r="E101" s="295"/>
-      <c r="F101" s="295"/>
-      <c r="G101" s="295"/>
-      <c r="H101" s="295"/>
-      <c r="I101" s="295"/>
+      <c r="D101" s="323"/>
+      <c r="E101" s="323"/>
+      <c r="F101" s="323"/>
+      <c r="G101" s="323"/>
+      <c r="H101" s="323"/>
+      <c r="I101" s="323"/>
       <c r="K101" s="33"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>29</v>
       </c>
@@ -5326,14 +5295,14 @@
         <v>0</v>
       </c>
       <c r="C102" s="13"/>
-      <c r="D102" s="295"/>
-      <c r="E102" s="295"/>
-      <c r="F102" s="295"/>
-      <c r="G102" s="295"/>
-      <c r="H102" s="295"/>
-      <c r="I102" s="295"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D102" s="323"/>
+      <c r="E102" s="323"/>
+      <c r="F102" s="323"/>
+      <c r="G102" s="323"/>
+      <c r="H102" s="323"/>
+      <c r="I102" s="323"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>35</v>
       </c>
@@ -5342,14 +5311,14 @@
         <v>0</v>
       </c>
       <c r="C103" s="13"/>
-      <c r="D103" s="295"/>
-      <c r="E103" s="295"/>
-      <c r="F103" s="295"/>
-      <c r="G103" s="295"/>
-      <c r="H103" s="295"/>
-      <c r="I103" s="295"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D103" s="323"/>
+      <c r="E103" s="323"/>
+      <c r="F103" s="323"/>
+      <c r="G103" s="323"/>
+      <c r="H103" s="323"/>
+      <c r="I103" s="323"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>22</v>
       </c>
@@ -5358,37 +5327,37 @@
         <v>6810425.1022069966</v>
       </c>
       <c r="C104" s="44"/>
-      <c r="D104" s="295"/>
-      <c r="E104" s="295"/>
-      <c r="F104" s="295"/>
-      <c r="G104" s="295"/>
-      <c r="H104" s="295"/>
-      <c r="I104" s="295"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D104" s="323"/>
+      <c r="E104" s="323"/>
+      <c r="F104" s="323"/>
+      <c r="G104" s="323"/>
+      <c r="H104" s="323"/>
+      <c r="I104" s="323"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="C105" s="9"/>
-      <c r="D105" s="295"/>
-      <c r="E105" s="295"/>
-      <c r="F105" s="295"/>
-      <c r="G105" s="295"/>
-      <c r="H105" s="295"/>
-      <c r="I105" s="295"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D105" s="323"/>
+      <c r="E105" s="323"/>
+      <c r="F105" s="323"/>
+      <c r="G105" s="323"/>
+      <c r="H105" s="323"/>
+      <c r="I105" s="323"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>265</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="9"/>
-      <c r="D106" s="295"/>
-      <c r="E106" s="295"/>
-      <c r="F106" s="295"/>
-      <c r="G106" s="295"/>
-      <c r="H106" s="295"/>
-      <c r="I106" s="295"/>
-    </row>
-    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D106" s="323"/>
+      <c r="E106" s="323"/>
+      <c r="F106" s="323"/>
+      <c r="G106" s="323"/>
+      <c r="H106" s="323"/>
+      <c r="I106" s="323"/>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="177"/>
       <c r="B107" s="21">
         <v>0</v>
@@ -5397,7 +5366,7 @@
       <c r="D107" s="16"/>
       <c r="E107" s="16"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="s">
         <v>15</v>
       </c>
@@ -5408,17 +5377,17 @@
       <c r="C108" s="9"/>
       <c r="E108" s="16"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="13"/>
       <c r="C109" s="9"/>
       <c r="D109" s="16"/>
     </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="C110" s="9"/>
       <c r="D110" s="16"/>
     </row>
-    <row r="111" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>18</v>
       </c>
@@ -5426,46 +5395,46 @@
         <v>-73817.72</v>
       </c>
       <c r="C111" s="9"/>
-      <c r="D111" s="316" t="s">
-        <v>426</v>
-      </c>
-      <c r="E111" s="317"/>
-      <c r="F111" s="317"/>
-      <c r="G111" s="317"/>
-      <c r="H111" s="317"/>
-      <c r="I111" s="318"/>
-    </row>
-    <row r="112" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D111" s="307" t="s">
+        <v>420</v>
+      </c>
+      <c r="E111" s="308"/>
+      <c r="F111" s="308"/>
+      <c r="G111" s="308"/>
+      <c r="H111" s="308"/>
+      <c r="I111" s="309"/>
+    </row>
+    <row r="112" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="179" t="s">
+        <v>402</v>
+      </c>
+      <c r="B112" s="239">
+        <v>-24000</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="310"/>
+      <c r="E112" s="311"/>
+      <c r="F112" s="311"/>
+      <c r="G112" s="311"/>
+      <c r="H112" s="311"/>
+      <c r="I112" s="312"/>
+    </row>
+    <row r="113" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="179" t="s">
         <v>408</v>
       </c>
-      <c r="B112" s="244">
-        <v>-24000</v>
-      </c>
-      <c r="C112" s="9"/>
-      <c r="D112" s="319"/>
-      <c r="E112" s="320"/>
-      <c r="F112" s="320"/>
-      <c r="G112" s="320"/>
-      <c r="H112" s="320"/>
-      <c r="I112" s="321"/>
-    </row>
-    <row r="113" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="179" t="s">
-        <v>414</v>
-      </c>
-      <c r="B113" s="244">
+      <c r="B113" s="239">
         <v>-1500</v>
       </c>
       <c r="C113" s="9"/>
-      <c r="D113" s="319"/>
-      <c r="E113" s="320"/>
-      <c r="F113" s="320"/>
-      <c r="G113" s="320"/>
-      <c r="H113" s="320"/>
-      <c r="I113" s="321"/>
-    </row>
-    <row r="114" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D113" s="310"/>
+      <c r="E113" s="311"/>
+      <c r="F113" s="311"/>
+      <c r="G113" s="311"/>
+      <c r="H113" s="311"/>
+      <c r="I113" s="312"/>
+    </row>
+    <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="24" t="s">
         <v>15</v>
       </c>
@@ -5474,31 +5443,31 @@
         <v>-97817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="322"/>
-      <c r="E114" s="323"/>
-      <c r="F114" s="323"/>
-      <c r="G114" s="323"/>
-      <c r="H114" s="323"/>
-      <c r="I114" s="324"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D114" s="313"/>
+      <c r="E114" s="314"/>
+      <c r="F114" s="314"/>
+      <c r="G114" s="314"/>
+      <c r="H114" s="314"/>
+      <c r="I114" s="315"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="13"/>
       <c r="F116" s="46"/>
       <c r="G116" s="46"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="F117" s="46"/>
       <c r="G117" s="46"/>
     </row>
-    <row r="118" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H118" s="55"/>
       <c r="I118" s="55"/>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>348</v>
       </c>
@@ -5506,17 +5475,17 @@
         <v>598840</v>
       </c>
       <c r="C119" s="15"/>
-      <c r="D119" s="296" t="s">
-        <v>418</v>
-      </c>
-      <c r="E119" s="297"/>
-      <c r="F119" s="297"/>
-      <c r="G119" s="297"/>
-      <c r="H119" s="297"/>
-      <c r="I119" s="297"/>
-      <c r="J119" s="298"/>
-    </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D119" s="287" t="s">
+        <v>412</v>
+      </c>
+      <c r="E119" s="288"/>
+      <c r="F119" s="288"/>
+      <c r="G119" s="288"/>
+      <c r="H119" s="288"/>
+      <c r="I119" s="288"/>
+      <c r="J119" s="289"/>
+    </row>
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>235</v>
       </c>
@@ -5524,15 +5493,15 @@
         <v>0</v>
       </c>
       <c r="C120" s="15"/>
-      <c r="D120" s="299"/>
-      <c r="E120" s="300"/>
-      <c r="F120" s="300"/>
-      <c r="G120" s="300"/>
-      <c r="H120" s="300"/>
-      <c r="I120" s="300"/>
-      <c r="J120" s="301"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D120" s="290"/>
+      <c r="E120" s="291"/>
+      <c r="F120" s="291"/>
+      <c r="G120" s="291"/>
+      <c r="H120" s="291"/>
+      <c r="I120" s="291"/>
+      <c r="J120" s="292"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
         <v>15</v>
       </c>
@@ -5541,59 +5510,59 @@
         <v>598840</v>
       </c>
       <c r="C121" s="15"/>
-      <c r="D121" s="299"/>
-      <c r="E121" s="300"/>
-      <c r="F121" s="300"/>
-      <c r="G121" s="300"/>
-      <c r="H121" s="300"/>
-      <c r="I121" s="300"/>
-      <c r="J121" s="301"/>
-    </row>
-    <row r="122" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D121" s="290"/>
+      <c r="E121" s="291"/>
+      <c r="F121" s="291"/>
+      <c r="G121" s="291"/>
+      <c r="H121" s="291"/>
+      <c r="I121" s="291"/>
+      <c r="J121" s="292"/>
+    </row>
+    <row r="122" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C122" s="16"/>
-      <c r="D122" s="299"/>
-      <c r="E122" s="300"/>
-      <c r="F122" s="300"/>
-      <c r="G122" s="300"/>
-      <c r="H122" s="300"/>
-      <c r="I122" s="300"/>
-      <c r="J122" s="301"/>
-    </row>
-    <row r="123" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="305" t="s">
+      <c r="D122" s="290"/>
+      <c r="E122" s="291"/>
+      <c r="F122" s="291"/>
+      <c r="G122" s="291"/>
+      <c r="H122" s="291"/>
+      <c r="I122" s="291"/>
+      <c r="J122" s="292"/>
+    </row>
+    <row r="123" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="296" t="s">
         <v>349</v>
       </c>
-      <c r="B123" s="307">
+      <c r="B123" s="298">
         <f>B121+B104+B114</f>
         <v>7311447.3822069969</v>
       </c>
       <c r="C123" s="9"/>
-      <c r="D123" s="299"/>
-      <c r="E123" s="300"/>
-      <c r="F123" s="300"/>
-      <c r="G123" s="300"/>
-      <c r="H123" s="300"/>
-      <c r="I123" s="300"/>
-      <c r="J123" s="301"/>
-    </row>
-    <row r="124" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="306"/>
-      <c r="B124" s="308"/>
-      <c r="D124" s="302"/>
-      <c r="E124" s="303"/>
-      <c r="F124" s="303"/>
-      <c r="G124" s="303"/>
-      <c r="H124" s="303"/>
-      <c r="I124" s="303"/>
-      <c r="J124" s="304"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D123" s="290"/>
+      <c r="E123" s="291"/>
+      <c r="F123" s="291"/>
+      <c r="G123" s="291"/>
+      <c r="H123" s="291"/>
+      <c r="I123" s="291"/>
+      <c r="J123" s="292"/>
+    </row>
+    <row r="124" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="297"/>
+      <c r="B124" s="299"/>
+      <c r="D124" s="293"/>
+      <c r="E124" s="294"/>
+      <c r="F124" s="294"/>
+      <c r="G124" s="294"/>
+      <c r="H124" s="294"/>
+      <c r="I124" s="294"/>
+      <c r="J124" s="295"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B125" s="31"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B126" s="125"/>
     </row>
-    <row r="129" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C129" s="46"/>
       <c r="D129" s="46"/>
       <c r="E129" s="46"/>
@@ -5601,7 +5570,7 @@
       <c r="G129" s="46"/>
       <c r="H129" s="46"/>
     </row>
-    <row r="130" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C130" s="46"/>
       <c r="D130" s="46"/>
       <c r="E130" s="46"/>
@@ -5609,23 +5578,23 @@
       <c r="G130" s="46"/>
       <c r="H130" s="46"/>
     </row>
-    <row r="131" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C131" s="46"/>
-      <c r="D131" s="250"/>
+      <c r="D131" s="245"/>
       <c r="E131" s="46"/>
       <c r="F131" s="46"/>
       <c r="G131" s="46"/>
       <c r="H131" s="46"/>
     </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C132" s="46"/>
-      <c r="D132" s="250"/>
+      <c r="D132" s="245"/>
       <c r="E132" s="46"/>
       <c r="F132" s="46"/>
       <c r="G132" s="46"/>
       <c r="H132" s="46"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="46"/>
@@ -5633,7 +5602,7 @@
       <c r="G133" s="46"/>
       <c r="H133" s="46"/>
     </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C134" s="46"/>
       <c r="D134" s="46"/>
       <c r="E134" s="46"/>
@@ -5641,7 +5610,7 @@
       <c r="G134" s="46"/>
       <c r="H134" s="46"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C135" s="46"/>
       <c r="D135" s="46"/>
       <c r="E135" s="46"/>
@@ -5649,7 +5618,7 @@
       <c r="G135" s="46"/>
       <c r="H135" s="46"/>
     </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C136" s="46"/>
       <c r="D136" s="46"/>
       <c r="E136" s="46"/>
@@ -5657,7 +5626,7 @@
       <c r="G136" s="46"/>
       <c r="H136" s="46"/>
     </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C137" s="46"/>
       <c r="D137" s="46"/>
       <c r="E137" s="46"/>
@@ -5665,7 +5634,7 @@
       <c r="G137" s="46"/>
       <c r="H137" s="46"/>
     </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C138" s="46"/>
       <c r="D138" s="46"/>
       <c r="E138" s="46"/>
@@ -5673,7 +5642,7 @@
       <c r="G138" s="46"/>
       <c r="H138" s="46"/>
     </row>
-    <row r="139" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="46"/>
@@ -5689,9 +5658,6 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="D111:I114"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A67:B67"/>
@@ -5701,6 +5667,9 @@
     <mergeCell ref="A123:A124"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="D111:I114"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5711,37 +5680,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="368" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="362" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="369"/>
-      <c r="C1" s="369"/>
-      <c r="D1" s="369"/>
-      <c r="E1" s="369"/>
+      <c r="B1" s="363"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
       <c r="F1" s="103" t="s">
         <v>268</v>
       </c>
@@ -5753,20 +5722,20 @@
       <c r="L1" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="347">
+      <c r="M1" s="341">
         <f>RESUMEN!D76-N4</f>
         <v>18487963.84</v>
       </c>
-      <c r="N1" s="348"/>
+      <c r="N1" s="342"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="370"/>
-      <c r="B2" s="371"/>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="364"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
       <c r="F2" s="4" t="s">
         <v>267</v>
       </c>
@@ -5786,12 +5755,12 @@
       <c r="O2" s="105"/>
       <c r="P2" s="39"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="370"/>
-      <c r="B3" s="371"/>
-      <c r="C3" s="371"/>
-      <c r="D3" s="371"/>
-      <c r="E3" s="371"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="364"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5809,12 +5778,12 @@
       <c r="O3" s="105"/>
       <c r="P3" s="39"/>
     </row>
-    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="370"/>
-      <c r="B4" s="371"/>
-      <c r="C4" s="371"/>
-      <c r="D4" s="371"/>
-      <c r="E4" s="371"/>
+    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="364"/>
+      <c r="B4" s="365"/>
+      <c r="C4" s="365"/>
+      <c r="D4" s="365"/>
+      <c r="E4" s="365"/>
       <c r="F4" s="4" t="s">
         <v>269</v>
       </c>
@@ -5824,7 +5793,7 @@
       <c r="J4" s="106"/>
       <c r="K4" s="106"/>
       <c r="L4" s="133" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="159">
@@ -5833,12 +5802,12 @@
       <c r="O4" s="107"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="372"/>
-      <c r="B5" s="373"/>
-      <c r="C5" s="373"/>
-      <c r="D5" s="373"/>
-      <c r="E5" s="373"/>
+    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="366"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="367"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5851,98 +5820,98 @@
       <c r="O5" s="111"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="347" t="s">
         <v>358</v>
       </c>
-      <c r="D6" s="354"/>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
-      <c r="G6" s="354"/>
-      <c r="H6" s="354"/>
-      <c r="I6" s="354"/>
-      <c r="J6" s="354"/>
-      <c r="K6" s="354"/>
-      <c r="L6" s="354"/>
-      <c r="M6" s="354"/>
-      <c r="N6" s="354"/>
-      <c r="O6" s="355"/>
+      <c r="D6" s="348"/>
+      <c r="E6" s="348"/>
+      <c r="F6" s="348"/>
+      <c r="G6" s="348"/>
+      <c r="H6" s="348"/>
+      <c r="I6" s="348"/>
+      <c r="J6" s="348"/>
+      <c r="K6" s="348"/>
+      <c r="L6" s="348"/>
+      <c r="M6" s="348"/>
+      <c r="N6" s="348"/>
+      <c r="O6" s="349"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="356"/>
-      <c r="D7" s="357"/>
-      <c r="E7" s="357"/>
-      <c r="F7" s="357"/>
-      <c r="G7" s="357"/>
-      <c r="H7" s="357"/>
-      <c r="I7" s="357"/>
-      <c r="J7" s="357"/>
-      <c r="K7" s="357"/>
-      <c r="L7" s="357"/>
-      <c r="M7" s="357"/>
-      <c r="N7" s="357"/>
-      <c r="O7" s="358"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="351"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
+      <c r="G7" s="351"/>
+      <c r="H7" s="351"/>
+      <c r="I7" s="351"/>
+      <c r="J7" s="351"/>
+      <c r="K7" s="351"/>
+      <c r="L7" s="351"/>
+      <c r="M7" s="351"/>
+      <c r="N7" s="351"/>
+      <c r="O7" s="352"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="356"/>
-      <c r="D8" s="357"/>
-      <c r="E8" s="357"/>
-      <c r="F8" s="357"/>
-      <c r="G8" s="357"/>
-      <c r="H8" s="357"/>
-      <c r="I8" s="357"/>
-      <c r="J8" s="357"/>
-      <c r="K8" s="357"/>
-      <c r="L8" s="357"/>
-      <c r="M8" s="357"/>
-      <c r="N8" s="357"/>
-      <c r="O8" s="358"/>
+      <c r="C8" s="350"/>
+      <c r="D8" s="351"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
+      <c r="G8" s="351"/>
+      <c r="H8" s="351"/>
+      <c r="I8" s="351"/>
+      <c r="J8" s="351"/>
+      <c r="K8" s="351"/>
+      <c r="L8" s="351"/>
+      <c r="M8" s="351"/>
+      <c r="N8" s="351"/>
+      <c r="O8" s="352"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="359"/>
-      <c r="D9" s="360"/>
-      <c r="E9" s="360"/>
-      <c r="F9" s="360"/>
-      <c r="G9" s="360"/>
-      <c r="H9" s="360"/>
-      <c r="I9" s="360"/>
-      <c r="J9" s="360"/>
-      <c r="K9" s="360"/>
-      <c r="L9" s="360"/>
-      <c r="M9" s="360"/>
-      <c r="N9" s="360"/>
-      <c r="O9" s="361"/>
+      <c r="C9" s="353"/>
+      <c r="D9" s="354"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
+      <c r="G9" s="354"/>
+      <c r="H9" s="354"/>
+      <c r="I9" s="354"/>
+      <c r="J9" s="354"/>
+      <c r="K9" s="354"/>
+      <c r="L9" s="354"/>
+      <c r="M9" s="354"/>
+      <c r="N9" s="354"/>
+      <c r="O9" s="355"/>
       <c r="Q9" s="55"/>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="362" t="s">
+      <c r="C10" s="356" t="s">
         <v>280</v>
       </c>
-      <c r="D10" s="363"/>
-      <c r="E10" s="363"/>
-      <c r="F10" s="363"/>
-      <c r="G10" s="363"/>
-      <c r="H10" s="363"/>
-      <c r="I10" s="363"/>
-      <c r="J10" s="363"/>
-      <c r="K10" s="363"/>
-      <c r="L10" s="363"/>
-      <c r="M10" s="363"/>
-      <c r="N10" s="363"/>
-      <c r="O10" s="364"/>
+      <c r="D10" s="357"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
+      <c r="G10" s="357"/>
+      <c r="H10" s="357"/>
+      <c r="I10" s="357"/>
+      <c r="J10" s="357"/>
+      <c r="K10" s="357"/>
+      <c r="L10" s="357"/>
+      <c r="M10" s="357"/>
+      <c r="N10" s="357"/>
+      <c r="O10" s="358"/>
       <c r="Q10" t="s">
         <v>230</v>
       </c>
@@ -5951,22 +5920,22 @@
         <v>271028.77927200001</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="365"/>
-      <c r="D11" s="366"/>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
-      <c r="G11" s="366"/>
-      <c r="H11" s="366"/>
-      <c r="I11" s="366"/>
-      <c r="J11" s="366"/>
-      <c r="K11" s="366"/>
-      <c r="L11" s="366"/>
-      <c r="M11" s="366"/>
-      <c r="N11" s="366"/>
-      <c r="O11" s="367"/>
+      <c r="C11" s="359"/>
+      <c r="D11" s="360"/>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="G11" s="360"/>
+      <c r="H11" s="360"/>
+      <c r="I11" s="360"/>
+      <c r="J11" s="360"/>
+      <c r="K11" s="360"/>
+      <c r="L11" s="360"/>
+      <c r="M11" s="360"/>
+      <c r="N11" s="360"/>
+      <c r="O11" s="361"/>
       <c r="Q11" t="s">
         <v>231</v>
       </c>
@@ -5975,50 +5944,50 @@
         <v>321219.29395200004</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="338" t="s">
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="332" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="334" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="338" t="s">
+      <c r="C12" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="342" t="s">
+      <c r="D12" s="336" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="342" t="s">
+      <c r="E12" s="336" t="s">
         <v>246</v>
       </c>
-      <c r="F12" s="338" t="s">
+      <c r="F12" s="332" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="338" t="s">
+      <c r="G12" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="338" t="s">
+      <c r="H12" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="349" t="s">
+      <c r="I12" s="343" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="335" t="s">
+      <c r="J12" s="329" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="335" t="s">
-        <v>427</v>
-      </c>
-      <c r="L12" s="335" t="s">
+      <c r="K12" s="329" t="s">
+        <v>421</v>
+      </c>
+      <c r="L12" s="329" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="351" t="s">
+      <c r="M12" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="335" t="s">
+      <c r="N12" s="329" t="s">
         <v>256</v>
       </c>
-      <c r="O12" s="335" t="s">
+      <c r="O12" s="329" t="s">
         <v>255</v>
       </c>
       <c r="Q12" t="s">
@@ -6029,22 +5998,22 @@
         <v>303652.61381399992</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="339"/>
-      <c r="B13" s="341"/>
-      <c r="C13" s="339"/>
-      <c r="D13" s="343"/>
-      <c r="E13" s="343"/>
-      <c r="F13" s="339"/>
-      <c r="G13" s="339"/>
-      <c r="H13" s="339"/>
-      <c r="I13" s="350"/>
-      <c r="J13" s="336"/>
-      <c r="K13" s="336"/>
-      <c r="L13" s="336"/>
-      <c r="M13" s="352"/>
-      <c r="N13" s="336"/>
-      <c r="O13" s="336"/>
+    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="333"/>
+      <c r="B13" s="335"/>
+      <c r="C13" s="333"/>
+      <c r="D13" s="337"/>
+      <c r="E13" s="337"/>
+      <c r="F13" s="333"/>
+      <c r="G13" s="333"/>
+      <c r="H13" s="333"/>
+      <c r="I13" s="344"/>
+      <c r="J13" s="330"/>
+      <c r="K13" s="330"/>
+      <c r="L13" s="330"/>
+      <c r="M13" s="346"/>
+      <c r="N13" s="330"/>
+      <c r="O13" s="330"/>
       <c r="Q13" t="s">
         <v>233</v>
       </c>
@@ -6053,20 +6022,20 @@
         <v>373919.33436599997</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="339"/>
-      <c r="B14" s="341"/>
-      <c r="C14" s="339"/>
-      <c r="D14" s="343"/>
-      <c r="E14" s="343"/>
-      <c r="F14" s="339"/>
-      <c r="G14" s="339"/>
-      <c r="H14" s="339"/>
-      <c r="I14" s="350"/>
-      <c r="J14" s="336"/>
-      <c r="K14" s="337"/>
-      <c r="L14" s="337"/>
-      <c r="M14" s="352"/>
+    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="333"/>
+      <c r="B14" s="335"/>
+      <c r="C14" s="333"/>
+      <c r="D14" s="337"/>
+      <c r="E14" s="337"/>
+      <c r="F14" s="333"/>
+      <c r="G14" s="333"/>
+      <c r="H14" s="333"/>
+      <c r="I14" s="344"/>
+      <c r="J14" s="330"/>
+      <c r="K14" s="331"/>
+      <c r="L14" s="331"/>
+      <c r="M14" s="346"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/10</v>
@@ -6083,7 +6052,7 @@
         <v>436657.47771599999</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="176" t="s">
         <v>113</v>
       </c>
@@ -6133,10 +6102,10 @@
       <c r="P15" s="70" t="s">
         <v>335</v>
       </c>
-      <c r="R15" s="344"/>
-      <c r="S15" s="344"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="338"/>
+      <c r="S15" s="338"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="23" t="s">
@@ -6181,10 +6150,10 @@
       <c r="P16" s="70" t="s">
         <v>334</v>
       </c>
-      <c r="R16" s="344"/>
-      <c r="S16" s="344"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R16" s="338"/>
+      <c r="S16" s="338"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>113</v>
       </c>
@@ -6193,7 +6162,7 @@
         <v>109</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E17" s="64" t="s">
         <v>289</v>
@@ -6201,7 +6170,7 @@
       <c r="F17" s="93">
         <v>1.21E-2</v>
       </c>
-      <c r="G17" s="245">
+      <c r="G17" s="240">
         <v>299898.61410299997</v>
       </c>
       <c r="H17" s="32">
@@ -6233,7 +6202,7 @@
       <c r="P17" s="70"/>
       <c r="S17" s="31"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>113</v>
       </c>
@@ -6265,7 +6234,7 @@
       <c r="L18" s="229">
         <v>373919.33436599997</v>
       </c>
-      <c r="M18" s="258">
+      <c r="M18" s="253">
         <v>0</v>
       </c>
       <c r="N18" s="221">
@@ -6279,28 +6248,28 @@
       <c r="P18" s="70"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="246" t="s">
+      <c r="C19" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="247" t="s">
+      <c r="D19" s="242" t="s">
         <v>245</v>
       </c>
-      <c r="E19" s="247"/>
+      <c r="E19" s="242"/>
       <c r="F19" s="98">
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="G19" s="99">
         <v>727422.31177599984</v>
       </c>
-      <c r="H19" s="409">
+      <c r="H19" s="282">
         <v>374000</v>
       </c>
-      <c r="I19" s="248">
+      <c r="I19" s="243">
         <f t="shared" si="0"/>
         <v>353422.31177599984</v>
       </c>
@@ -6313,7 +6282,7 @@
       <c r="L19" s="99">
         <v>436657.47771599999</v>
       </c>
-      <c r="M19" s="249">
+      <c r="M19" s="244">
         <v>0</v>
       </c>
       <c r="N19" s="96">
@@ -6327,7 +6296,7 @@
       <c r="P19" s="70"/>
       <c r="S19" s="31"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
         <v>115</v>
       </c>
@@ -6378,52 +6347,52 @@
       </c>
       <c r="S20" s="31"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
         <v>116</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="281" t="s">
+      <c r="C21" s="269" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="282" t="s">
+      <c r="D21" s="270" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="283"/>
-      <c r="F21" s="284">
+      <c r="E21" s="271"/>
+      <c r="F21" s="272">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G21" s="285">
+      <c r="G21" s="273">
         <v>220298.02</v>
       </c>
-      <c r="H21" s="410">
+      <c r="H21" s="283">
         <f>G21</f>
         <v>220298.02</v>
       </c>
-      <c r="I21" s="286">
+      <c r="I21" s="274">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="287">
+      <c r="J21" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K21" s="288">
+      <c r="K21" s="276">
         <f t="shared" ref="K21:K84" si="5">N$4*F21</f>
         <v>64046.690399999999</v>
       </c>
-      <c r="L21" s="287">
+      <c r="L21" s="275">
         <f t="shared" ref="L21:L51" si="6">N$2*F21</f>
         <v>155298.89625599998</v>
       </c>
-      <c r="M21" s="289">
-        <v>0</v>
-      </c>
-      <c r="N21" s="290">
+      <c r="M21" s="277">
+        <v>0</v>
+      </c>
+      <c r="N21" s="278">
         <f t="shared" ref="N21:N84" si="7">ROUND((L21+J21+I21+K21+M21),0) + P21</f>
         <v>219346.02</v>
       </c>
-      <c r="O21" s="291">
+      <c r="O21" s="279">
         <f t="shared" ref="O21:O84" si="8">ROUND((N21*6% + N21 ),0) + P21</f>
         <v>232507.02</v>
       </c>
@@ -6433,7 +6402,7 @@
       </c>
       <c r="S21" s="31"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>115</v>
       </c>
@@ -6484,51 +6453,51 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
         <v>117</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="281" t="s">
+      <c r="C23" s="269" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="282" t="s">
-        <v>392</v>
-      </c>
-      <c r="E23" s="283" t="s">
+      <c r="D23" s="270" t="s">
+        <v>386</v>
+      </c>
+      <c r="E23" s="271" t="s">
         <v>261</v>
       </c>
-      <c r="F23" s="284">
+      <c r="F23" s="272">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G23" s="285">
+      <c r="G23" s="273">
         <v>246524.04</v>
       </c>
-      <c r="H23" s="410">
+      <c r="H23" s="283">
         <f>G23</f>
         <v>246524.04</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="274">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="287">
+      <c r="J23" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="288"/>
-      <c r="L23" s="287">
+      <c r="K23" s="276"/>
+      <c r="L23" s="275">
         <f t="shared" si="6"/>
         <v>173786.86009600002</v>
       </c>
-      <c r="M23" s="289">
-        <v>0</v>
-      </c>
-      <c r="N23" s="290">
+      <c r="M23" s="277">
+        <v>0</v>
+      </c>
+      <c r="N23" s="278">
         <f t="shared" si="7"/>
         <v>173787.04</v>
       </c>
-      <c r="O23" s="291">
+      <c r="O23" s="279">
         <f t="shared" si="8"/>
         <v>184214.04</v>
       </c>
@@ -6540,7 +6509,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>117</v>
       </c>
@@ -6595,7 +6564,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="37" t="s">
         <v>117</v>
       </c>
@@ -6604,7 +6573,7 @@
         <v>44</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E25" s="87" t="s">
         <v>273</v>
@@ -6648,7 +6617,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>115</v>
       </c>
@@ -6657,7 +6626,7 @@
         <v>45</v>
       </c>
       <c r="D26" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E26" s="87" t="s">
         <v>281</v>
@@ -6700,7 +6669,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
         <v>116</v>
       </c>
@@ -6754,51 +6723,51 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="64" t="s">
         <v>115</v>
       </c>
       <c r="B28" s="23"/>
-      <c r="C28" s="281" t="s">
+      <c r="C28" s="269" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="282" t="s">
-        <v>392</v>
-      </c>
-      <c r="E28" s="283" t="s">
+      <c r="D28" s="270" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" s="271" t="s">
         <v>291</v>
       </c>
-      <c r="F28" s="284">
+      <c r="F28" s="272">
         <v>1.78E-2</v>
       </c>
-      <c r="G28" s="285">
+      <c r="G28" s="273">
         <v>1109042.0900000001</v>
       </c>
-      <c r="H28" s="410">
+      <c r="H28" s="283">
         <f>728003.08+(526500-G118)</f>
         <v>1108399.0899999999</v>
       </c>
-      <c r="I28" s="286">
+      <c r="I28" s="274">
         <f t="shared" si="0"/>
         <v>643.00000000023283</v>
       </c>
-      <c r="J28" s="287">
+      <c r="J28" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K28" s="288"/>
-      <c r="L28" s="287">
+      <c r="K28" s="276"/>
+      <c r="L28" s="275">
         <f t="shared" si="6"/>
         <v>329085.756352</v>
       </c>
-      <c r="M28" s="289">
-        <v>0</v>
-      </c>
-      <c r="N28" s="290">
+      <c r="M28" s="277">
+        <v>0</v>
+      </c>
+      <c r="N28" s="278">
         <f t="shared" si="7"/>
         <v>329729.09000000003</v>
       </c>
-      <c r="O28" s="291">
+      <c r="O28" s="279">
         <f t="shared" si="8"/>
         <v>349513.09</v>
       </c>
@@ -6807,7 +6776,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="64" t="s">
         <v>117</v>
       </c>
@@ -6861,7 +6830,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="64" t="s">
         <v>117</v>
       </c>
@@ -6915,7 +6884,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="64" t="s">
         <v>117</v>
       </c>
@@ -6966,7 +6935,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="64" t="s">
         <v>115</v>
       </c>
@@ -7017,7 +6986,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
         <v>116</v>
       </c>
@@ -7026,7 +6995,7 @@
         <v>52</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E33" s="87" t="s">
         <v>248</v>
@@ -7069,7 +7038,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>115</v>
       </c>
@@ -7120,7 +7089,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="91" t="s">
         <v>117</v>
       </c>
@@ -7174,7 +7143,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="37" t="s">
         <v>117</v>
       </c>
@@ -7230,7 +7199,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="37" t="s">
         <v>117</v>
       </c>
@@ -7283,7 +7252,7 @@
       <c r="Q37" s="46"/>
       <c r="R37" s="46"/>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="64" t="s">
         <v>115</v>
       </c>
@@ -7339,7 +7308,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="64" t="s">
         <v>116</v>
       </c>
@@ -7392,7 +7361,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="64" t="s">
         <v>115</v>
       </c>
@@ -7401,7 +7370,7 @@
         <v>59</v>
       </c>
       <c r="D40" s="64" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E40" s="87"/>
       <c r="F40" s="88">
@@ -7543,7 +7512,7 @@
       <c r="DI40" s="46"/>
       <c r="DJ40" s="46"/>
     </row>
-    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="64" t="s">
         <v>117</v>
       </c>
@@ -7697,7 +7666,7 @@
       <c r="DI41" s="46"/>
       <c r="DJ41" s="46"/>
     </row>
-    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="64" t="s">
         <v>117</v>
       </c>
@@ -7851,7 +7820,7 @@
       <c r="DI42" s="46"/>
       <c r="DJ42" s="46"/>
     </row>
-    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="64" t="s">
         <v>117</v>
       </c>
@@ -7866,7 +7835,7 @@
       <c r="F43" s="88">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G43" s="408">
+      <c r="G43" s="281">
         <v>1453566.24</v>
       </c>
       <c r="H43" s="32">
@@ -8000,7 +7969,7 @@
       <c r="DI43" s="46"/>
       <c r="DJ43" s="46"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>115</v>
       </c>
@@ -8054,7 +8023,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>116</v>
       </c>
@@ -8107,7 +8076,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>115</v>
       </c>
@@ -8164,7 +8133,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="115" t="s">
         <v>117</v>
       </c>
@@ -8215,7 +8184,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>117</v>
       </c>
@@ -8271,7 +8240,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>117</v>
       </c>
@@ -8322,7 +8291,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
         <v>115</v>
       </c>
@@ -8331,7 +8300,7 @@
         <v>69</v>
       </c>
       <c r="D50" s="64" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E50" s="87"/>
       <c r="F50" s="88">
@@ -8373,7 +8342,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
         <v>116</v>
       </c>
@@ -8427,7 +8396,7 @@
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="37" t="s">
         <v>115</v>
       </c>
@@ -8436,7 +8405,7 @@
         <v>71</v>
       </c>
       <c r="D52" s="64" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E52" s="87"/>
       <c r="F52" s="88">
@@ -8479,7 +8448,7 @@
       </c>
       <c r="Q52" s="31"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>117</v>
       </c>
@@ -8535,7 +8504,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="37" t="s">
         <v>117</v>
       </c>
@@ -8586,7 +8555,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="64" t="s">
         <v>117</v>
       </c>
@@ -8640,7 +8609,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="37" t="s">
         <v>115</v>
       </c>
@@ -8649,7 +8618,7 @@
         <v>75</v>
       </c>
       <c r="D56" s="64" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E56" s="87"/>
       <c r="F56" s="88">
@@ -8692,7 +8661,7 @@
       </c>
       <c r="R56" s="39"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="37" t="s">
         <v>116</v>
       </c>
@@ -8745,7 +8714,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="37" t="s">
         <v>115</v>
       </c>
@@ -8754,7 +8723,7 @@
         <v>77</v>
       </c>
       <c r="D58" s="64" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E58" s="87"/>
       <c r="F58" s="88">
@@ -8796,7 +8765,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
         <v>117</v>
       </c>
@@ -8805,7 +8774,7 @@
         <v>78</v>
       </c>
       <c r="D59" s="64" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E59" s="87" t="s">
         <v>288</v>
@@ -8852,7 +8821,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="64" t="s">
         <v>117</v>
       </c>
@@ -8861,7 +8830,7 @@
         <v>79</v>
       </c>
       <c r="D60" s="64" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="E60" s="87"/>
       <c r="F60" s="88">
@@ -8909,7 +8878,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="64" t="s">
         <v>117</v>
       </c>
@@ -8918,7 +8887,7 @@
         <v>80</v>
       </c>
       <c r="D61" s="64" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E61" s="87"/>
       <c r="F61" s="88">
@@ -8963,7 +8932,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="64" t="s">
         <v>115</v>
       </c>
@@ -9014,7 +8983,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="64" t="s">
         <v>116</v>
       </c>
@@ -9065,52 +9034,52 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="64" t="s">
         <v>115</v>
       </c>
       <c r="B64" s="23"/>
-      <c r="C64" s="281" t="s">
+      <c r="C64" s="269" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="282" t="s">
+      <c r="D64" s="270" t="s">
         <v>195</v>
       </c>
-      <c r="E64" s="283"/>
-      <c r="F64" s="284">
+      <c r="E64" s="271"/>
+      <c r="F64" s="272">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G64" s="285">
+      <c r="G64" s="273">
         <v>473709.45</v>
       </c>
-      <c r="H64" s="410">
+      <c r="H64" s="283">
         <f>G64</f>
         <v>473709.45</v>
       </c>
-      <c r="I64" s="286">
+      <c r="I64" s="274">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J64" s="287">
+      <c r="J64" s="275">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K64" s="288">
+      <c r="K64" s="276">
         <f t="shared" si="5"/>
         <v>131905.6838</v>
       </c>
-      <c r="L64" s="287">
+      <c r="L64" s="275">
         <f t="shared" si="15"/>
         <v>319841.77443200001</v>
       </c>
-      <c r="M64" s="289">
-        <v>0</v>
-      </c>
-      <c r="N64" s="290">
+      <c r="M64" s="277">
+        <v>0</v>
+      </c>
+      <c r="N64" s="278">
         <f t="shared" si="7"/>
         <v>451747.45</v>
       </c>
-      <c r="O64" s="291">
+      <c r="O64" s="279">
         <f t="shared" si="8"/>
         <v>478852.45</v>
       </c>
@@ -9119,51 +9088,51 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="282" t="s">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" s="270" t="s">
         <v>117</v>
       </c>
-      <c r="B65" s="281"/>
-      <c r="C65" s="281" t="s">
+      <c r="B65" s="269"/>
+      <c r="C65" s="269" t="s">
         <v>84</v>
       </c>
-      <c r="D65" s="282" t="s">
+      <c r="D65" s="270" t="s">
         <v>196</v>
       </c>
-      <c r="E65" s="283" t="s">
+      <c r="E65" s="271" t="s">
         <v>357</v>
       </c>
-      <c r="F65" s="284">
+      <c r="F65" s="272">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G65" s="285">
+      <c r="G65" s="273">
         <v>261524.46</v>
       </c>
-      <c r="H65" s="410">
+      <c r="H65" s="283">
         <f>G65+15000</f>
         <v>276524.45999999996</v>
       </c>
-      <c r="I65" s="286">
+      <c r="I65" s="274">
         <f t="shared" si="0"/>
         <v>-14999.999999999971</v>
       </c>
-      <c r="J65" s="287">
+      <c r="J65" s="275">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K65" s="288"/>
-      <c r="L65" s="287">
+      <c r="K65" s="276"/>
+      <c r="L65" s="275">
         <f t="shared" si="15"/>
         <v>173786.86009600002</v>
       </c>
-      <c r="M65" s="289">
-        <v>0</v>
-      </c>
-      <c r="N65" s="290">
+      <c r="M65" s="277">
+        <v>0</v>
+      </c>
+      <c r="N65" s="278">
         <f t="shared" si="7"/>
         <v>158787.46</v>
       </c>
-      <c r="O65" s="291">
+      <c r="O65" s="279">
         <f t="shared" si="8"/>
         <v>168315.46</v>
       </c>
@@ -9172,7 +9141,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="64" t="s">
         <v>117</v>
       </c>
@@ -9226,7 +9195,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="64" t="s">
         <v>117</v>
       </c>
@@ -9278,7 +9247,7 @@
       </c>
       <c r="S67" s="125"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>115</v>
       </c>
@@ -9333,7 +9302,7 @@
       </c>
       <c r="S68" s="31"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="91" t="s">
         <v>116</v>
       </c>
@@ -9387,7 +9356,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="37" t="s">
         <v>115</v>
       </c>
@@ -9441,7 +9410,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="37" t="s">
         <v>117</v>
       </c>
@@ -9494,7 +9463,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="37" t="s">
         <v>117</v>
       </c>
@@ -9548,7 +9517,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="37" t="s">
         <v>117</v>
       </c>
@@ -9599,7 +9568,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="37" t="s">
         <v>118</v>
       </c>
@@ -9608,7 +9577,7 @@
         <v>93</v>
       </c>
       <c r="D74" s="64" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E74" s="87"/>
       <c r="F74" s="88">
@@ -9651,7 +9620,7 @@
       </c>
       <c r="Q74" s="46"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="37" t="s">
         <v>115</v>
       </c>
@@ -9702,7 +9671,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="37" t="s">
         <v>117</v>
       </c>
@@ -9711,7 +9680,7 @@
         <v>95</v>
       </c>
       <c r="D76" s="64" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E76" s="87"/>
       <c r="F76" s="88">
@@ -9756,7 +9725,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
         <v>117</v>
       </c>
@@ -9812,7 +9781,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>117</v>
       </c>
@@ -9862,7 +9831,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="64" t="s">
         <v>118</v>
       </c>
@@ -9916,7 +9885,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="37" t="s">
         <v>115</v>
       </c>
@@ -9925,7 +9894,7 @@
         <v>99</v>
       </c>
       <c r="D80" s="64" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E80" s="87"/>
       <c r="F80" s="88">
@@ -9967,7 +9936,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="37" t="s">
         <v>117</v>
       </c>
@@ -10020,7 +9989,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="37" t="s">
         <v>117</v>
       </c>
@@ -10073,7 +10042,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="37" t="s">
         <v>117</v>
       </c>
@@ -10130,7 +10099,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="37" t="s">
         <v>118</v>
       </c>
@@ -10139,7 +10108,7 @@
         <v>103</v>
       </c>
       <c r="D84" s="64" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E84" s="87"/>
       <c r="F84" s="88">
@@ -10182,16 +10151,16 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="37" t="s">
         <v>115</v>
       </c>
       <c r="B85" s="3"/>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="114" t="s">
         <v>104</v>
       </c>
-      <c r="D85" s="64" t="s">
-        <v>403</v>
+      <c r="D85" s="115" t="s">
+        <v>397</v>
       </c>
       <c r="E85" s="87"/>
       <c r="F85" s="88">
@@ -10231,7 +10200,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="37" t="s">
         <v>117</v>
       </c>
@@ -10280,7 +10249,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="37" t="s">
         <v>117</v>
       </c>
@@ -10329,7 +10298,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="64" t="s">
         <v>117</v>
       </c>
@@ -10360,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="129">
-        <f t="shared" ref="K85:K132" si="26">N$4*F88</f>
+        <f t="shared" ref="K88:K131" si="26">N$4*F88</f>
         <v>72433.756999999998</v>
       </c>
       <c r="L88" s="95">
@@ -10383,7 +10352,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="64"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23" t="s">
@@ -10430,7 +10399,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="64"/>
       <c r="B90" s="23"/>
       <c r="C90" s="23" t="s">
@@ -10482,7 +10451,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="64"/>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
@@ -10534,7 +10503,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="64"/>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -10586,14 +10555,14 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="64"/>
       <c r="B93" s="23"/>
       <c r="C93" s="119" t="s">
         <v>123</v>
       </c>
       <c r="D93" s="120" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E93" s="120"/>
       <c r="F93" s="121">
@@ -10641,14 +10610,14 @@
         <v>257</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="64"/>
       <c r="B94" s="23"/>
       <c r="C94" s="23" t="s">
         <v>124</v>
       </c>
       <c r="D94" s="64" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E94" s="64"/>
       <c r="F94" s="93">
@@ -10690,14 +10659,14 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="64"/>
       <c r="B95" s="23"/>
       <c r="C95" s="23" t="s">
         <v>125</v>
       </c>
       <c r="D95" s="64" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E95" s="64"/>
       <c r="F95" s="93">
@@ -10739,7 +10708,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23" t="s">
@@ -10788,14 +10757,14 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
       <c r="B97" s="23"/>
       <c r="C97" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D97" s="64" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E97" s="64"/>
       <c r="F97" s="93">
@@ -10837,7 +10806,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
       <c r="B98" s="23"/>
       <c r="C98" s="23" t="s">
@@ -10885,7 +10854,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="64"/>
       <c r="B99" s="23"/>
       <c r="C99" s="23" t="s">
@@ -10934,7 +10903,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="64"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23" t="s">
@@ -10986,7 +10955,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="64"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23" t="s">
@@ -11035,14 +11004,14 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="64"/>
       <c r="B102" s="23"/>
       <c r="C102" s="23" t="s">
         <v>132</v>
       </c>
       <c r="D102" s="64" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E102" s="64"/>
       <c r="F102" s="93">
@@ -11084,14 +11053,14 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64"/>
       <c r="B103" s="23"/>
       <c r="C103" s="23" t="s">
         <v>133</v>
       </c>
       <c r="D103" s="64" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E103" s="64"/>
       <c r="F103" s="93">
@@ -11136,7 +11105,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23" t="s">
@@ -11187,7 +11156,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="64"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23" t="s">
@@ -11239,7 +11208,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="64"/>
       <c r="B106" s="23"/>
       <c r="C106" s="23" t="s">
@@ -11291,14 +11260,14 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="64"/>
       <c r="B107" s="23"/>
       <c r="C107" s="23" t="s">
         <v>137</v>
       </c>
       <c r="D107" s="64" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E107" s="64"/>
       <c r="F107" s="59">
@@ -11339,14 +11308,14 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="64"/>
       <c r="B108" s="23"/>
       <c r="C108" s="23" t="s">
         <v>138</v>
       </c>
       <c r="D108" s="64" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E108" s="64"/>
       <c r="F108" s="59">
@@ -11388,14 +11357,14 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="64"/>
       <c r="B109" s="23"/>
       <c r="C109" s="23" t="s">
         <v>139</v>
       </c>
       <c r="D109" s="64" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E109" s="64"/>
       <c r="F109" s="59">
@@ -11440,7 +11409,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="64"/>
       <c r="B110" s="23"/>
       <c r="C110" s="23" t="s">
@@ -11489,7 +11458,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="64"/>
       <c r="B111" s="23"/>
       <c r="C111" s="222" t="s">
@@ -11540,14 +11509,14 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="64"/>
       <c r="B112" s="23"/>
       <c r="C112" s="23" t="s">
         <v>142</v>
       </c>
       <c r="D112" s="64" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E112" s="64"/>
       <c r="F112" s="93">
@@ -11589,7 +11558,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="64"/>
       <c r="B113" s="23"/>
       <c r="C113" s="23" t="s">
@@ -11638,7 +11607,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="64"/>
       <c r="B114" s="23"/>
       <c r="C114" s="23" t="s">
@@ -11687,7 +11656,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="64"/>
       <c r="B115" s="23"/>
       <c r="C115" s="23" t="s">
@@ -11736,7 +11705,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="64"/>
       <c r="B116" s="23"/>
       <c r="C116" s="23" t="s">
@@ -11785,14 +11754,14 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="64"/>
       <c r="B117" s="23"/>
       <c r="C117" s="23" t="s">
         <v>147</v>
       </c>
       <c r="D117" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E117" s="64" t="s">
         <v>281</v>
@@ -11835,14 +11804,14 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="64"/>
       <c r="B118" s="23"/>
       <c r="C118" s="23" t="s">
         <v>148</v>
       </c>
       <c r="D118" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E118" s="64" t="s">
         <v>345</v>
@@ -11886,7 +11855,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="64"/>
       <c r="B119" s="23"/>
       <c r="C119" s="23" t="s">
@@ -11943,13 +11912,13 @@
         <v>272</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="80"/>
       <c r="B120" s="23"/>
-      <c r="C120" s="23" t="s">
+      <c r="C120" s="285" t="s">
         <v>150</v>
       </c>
-      <c r="D120" s="64" t="s">
+      <c r="D120" s="286" t="s">
         <v>270</v>
       </c>
       <c r="E120" s="64"/>
@@ -11995,7 +11964,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="80"/>
       <c r="B121" s="23"/>
       <c r="C121" s="23" t="s">
@@ -12044,14 +12013,14 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="80"/>
       <c r="B122" s="23"/>
       <c r="C122" s="23" t="s">
         <v>152</v>
       </c>
       <c r="D122" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E122" s="64" t="s">
         <v>346</v>
@@ -12098,13 +12067,13 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="80"/>
       <c r="B123" s="23"/>
-      <c r="C123" s="23" t="s">
+      <c r="C123" s="411" t="s">
         <v>153</v>
       </c>
-      <c r="D123" s="64" t="s">
+      <c r="D123" s="412" t="s">
         <v>212</v>
       </c>
       <c r="E123" s="64"/>
@@ -12147,7 +12116,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="80"/>
       <c r="B124" s="23"/>
       <c r="C124" s="23" t="s">
@@ -12199,14 +12168,14 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="80"/>
       <c r="B125" s="23"/>
       <c r="C125" s="23" t="s">
         <v>155</v>
       </c>
       <c r="D125" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E125" s="64"/>
       <c r="F125" s="93">
@@ -12254,14 +12223,14 @@
         <v>286</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="118"/>
       <c r="B126" s="113"/>
       <c r="C126" s="23" t="s">
         <v>156</v>
       </c>
       <c r="D126" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E126" s="87" t="s">
         <v>262</v>
@@ -12305,14 +12274,14 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="118"/>
       <c r="B127" s="113"/>
       <c r="C127" s="23" t="s">
         <v>157</v>
       </c>
       <c r="D127" s="64" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E127" s="64"/>
       <c r="F127" s="93">
@@ -12353,7 +12322,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="80"/>
       <c r="B128" s="23"/>
       <c r="C128" s="23" t="s">
@@ -12404,7 +12373,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="80"/>
       <c r="B129" s="23"/>
       <c r="C129" s="23" t="s">
@@ -12453,7 +12422,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="80"/>
       <c r="B130" s="23"/>
       <c r="C130" s="23" t="s">
@@ -12502,7 +12471,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="80" t="s">
         <v>23</v>
       </c>
@@ -12556,7 +12525,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="80" t="s">
         <v>23</v>
       </c>
@@ -12607,7 +12576,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="34" t="s">
         <v>23</v>
       </c>
@@ -12626,7 +12595,7 @@
       <c r="N133" s="2"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="18"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
@@ -12671,43 +12640,43 @@
       </c>
       <c r="Q134" s="39"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L135" s="41">
         <f>L134-M1</f>
         <v>412320.03031993657</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="346"/>
-      <c r="D136" s="346"/>
-      <c r="E136" s="346"/>
-      <c r="F136" s="346"/>
-      <c r="G136" s="346"/>
-      <c r="H136" s="346"/>
-      <c r="I136" s="346"/>
-      <c r="J136" s="346"/>
-      <c r="K136" s="346"/>
-      <c r="L136" s="346"/>
-      <c r="M136" s="346"/>
-      <c r="N136" s="346"/>
-      <c r="O136" s="346"/>
-    </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="346"/>
-      <c r="D137" s="346"/>
-      <c r="E137" s="346"/>
-      <c r="F137" s="346"/>
-      <c r="G137" s="346"/>
-      <c r="H137" s="346"/>
-      <c r="I137" s="346"/>
-      <c r="J137" s="346"/>
-      <c r="K137" s="346"/>
-      <c r="L137" s="346"/>
-      <c r="M137" s="346"/>
-      <c r="N137" s="346"/>
-      <c r="O137" s="346"/>
-    </row>
-    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="340"/>
+      <c r="D136" s="340"/>
+      <c r="E136" s="340"/>
+      <c r="F136" s="340"/>
+      <c r="G136" s="340"/>
+      <c r="H136" s="340"/>
+      <c r="I136" s="340"/>
+      <c r="J136" s="340"/>
+      <c r="K136" s="340"/>
+      <c r="L136" s="340"/>
+      <c r="M136" s="340"/>
+      <c r="N136" s="340"/>
+      <c r="O136" s="340"/>
+    </row>
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C137" s="340"/>
+      <c r="D137" s="340"/>
+      <c r="E137" s="340"/>
+      <c r="F137" s="340"/>
+      <c r="G137" s="340"/>
+      <c r="H137" s="340"/>
+      <c r="I137" s="340"/>
+      <c r="J137" s="340"/>
+      <c r="K137" s="340"/>
+      <c r="L137" s="340"/>
+      <c r="M137" s="340"/>
+      <c r="N137" s="340"/>
+      <c r="O137" s="340"/>
+    </row>
+    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
       <c r="E138" s="49"/>
@@ -12722,129 +12691,129 @@
       <c r="N138" s="49"/>
       <c r="O138" s="49"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="295" t="s">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C139" s="323" t="s">
         <v>239</v>
       </c>
-      <c r="D139" s="295"/>
-      <c r="E139" s="295"/>
-      <c r="F139" s="295"/>
-      <c r="G139" s="295"/>
-      <c r="H139" s="295"/>
-      <c r="I139" s="295"/>
-      <c r="J139" s="295"/>
-      <c r="K139" s="295"/>
-      <c r="L139" s="295"/>
-      <c r="M139" s="295"/>
-      <c r="N139" s="295"/>
-      <c r="O139" s="295"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="295"/>
-      <c r="D140" s="295"/>
-      <c r="E140" s="295"/>
-      <c r="F140" s="295"/>
-      <c r="G140" s="295"/>
-      <c r="H140" s="295"/>
-      <c r="I140" s="295"/>
-      <c r="J140" s="295"/>
-      <c r="K140" s="295"/>
-      <c r="L140" s="295"/>
-      <c r="M140" s="295"/>
-      <c r="N140" s="295"/>
-      <c r="O140" s="295"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="295"/>
-      <c r="D141" s="295"/>
-      <c r="E141" s="295"/>
-      <c r="F141" s="295"/>
-      <c r="G141" s="295"/>
-      <c r="H141" s="295"/>
-      <c r="I141" s="295"/>
-      <c r="J141" s="295"/>
-      <c r="K141" s="295"/>
-      <c r="L141" s="295"/>
-      <c r="M141" s="295"/>
-      <c r="N141" s="295"/>
-      <c r="O141" s="295"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="295"/>
-      <c r="D142" s="295"/>
-      <c r="E142" s="295"/>
-      <c r="F142" s="295"/>
-      <c r="G142" s="295"/>
-      <c r="H142" s="295"/>
-      <c r="I142" s="295"/>
-      <c r="J142" s="295"/>
-      <c r="K142" s="295"/>
-      <c r="L142" s="295"/>
-      <c r="M142" s="295"/>
-      <c r="N142" s="295"/>
-      <c r="O142" s="295"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="295"/>
-      <c r="D143" s="295"/>
-      <c r="E143" s="295"/>
-      <c r="F143" s="295"/>
-      <c r="G143" s="295"/>
-      <c r="H143" s="295"/>
-      <c r="I143" s="295"/>
-      <c r="J143" s="295"/>
-      <c r="K143" s="295"/>
-      <c r="L143" s="295"/>
-      <c r="M143" s="295"/>
-      <c r="N143" s="295"/>
-      <c r="O143" s="295"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="295"/>
-      <c r="D144" s="295"/>
-      <c r="E144" s="295"/>
-      <c r="F144" s="295"/>
-      <c r="G144" s="295"/>
-      <c r="H144" s="295"/>
-      <c r="I144" s="295"/>
-      <c r="J144" s="295"/>
-      <c r="K144" s="295"/>
-      <c r="L144" s="295"/>
-      <c r="M144" s="295"/>
-      <c r="N144" s="295"/>
-      <c r="O144" s="295"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="295"/>
-      <c r="D145" s="295"/>
-      <c r="E145" s="295"/>
-      <c r="F145" s="295"/>
-      <c r="G145" s="295"/>
-      <c r="H145" s="295"/>
-      <c r="I145" s="295"/>
-      <c r="J145" s="295"/>
-      <c r="K145" s="295"/>
-      <c r="L145" s="295"/>
-      <c r="M145" s="295"/>
-      <c r="N145" s="295"/>
-      <c r="O145" s="295"/>
-    </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C146" s="295"/>
-      <c r="D146" s="295"/>
-      <c r="E146" s="295"/>
-      <c r="F146" s="295"/>
-      <c r="G146" s="295"/>
-      <c r="H146" s="295"/>
-      <c r="I146" s="295"/>
-      <c r="J146" s="295"/>
-      <c r="K146" s="295"/>
-      <c r="L146" s="295"/>
-      <c r="M146" s="295"/>
-      <c r="N146" s="295"/>
-      <c r="O146" s="295"/>
-    </row>
-    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D139" s="323"/>
+      <c r="E139" s="323"/>
+      <c r="F139" s="323"/>
+      <c r="G139" s="323"/>
+      <c r="H139" s="323"/>
+      <c r="I139" s="323"/>
+      <c r="J139" s="323"/>
+      <c r="K139" s="323"/>
+      <c r="L139" s="323"/>
+      <c r="M139" s="323"/>
+      <c r="N139" s="323"/>
+      <c r="O139" s="323"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="323"/>
+      <c r="D140" s="323"/>
+      <c r="E140" s="323"/>
+      <c r="F140" s="323"/>
+      <c r="G140" s="323"/>
+      <c r="H140" s="323"/>
+      <c r="I140" s="323"/>
+      <c r="J140" s="323"/>
+      <c r="K140" s="323"/>
+      <c r="L140" s="323"/>
+      <c r="M140" s="323"/>
+      <c r="N140" s="323"/>
+      <c r="O140" s="323"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C141" s="323"/>
+      <c r="D141" s="323"/>
+      <c r="E141" s="323"/>
+      <c r="F141" s="323"/>
+      <c r="G141" s="323"/>
+      <c r="H141" s="323"/>
+      <c r="I141" s="323"/>
+      <c r="J141" s="323"/>
+      <c r="K141" s="323"/>
+      <c r="L141" s="323"/>
+      <c r="M141" s="323"/>
+      <c r="N141" s="323"/>
+      <c r="O141" s="323"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C142" s="323"/>
+      <c r="D142" s="323"/>
+      <c r="E142" s="323"/>
+      <c r="F142" s="323"/>
+      <c r="G142" s="323"/>
+      <c r="H142" s="323"/>
+      <c r="I142" s="323"/>
+      <c r="J142" s="323"/>
+      <c r="K142" s="323"/>
+      <c r="L142" s="323"/>
+      <c r="M142" s="323"/>
+      <c r="N142" s="323"/>
+      <c r="O142" s="323"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="323"/>
+      <c r="D143" s="323"/>
+      <c r="E143" s="323"/>
+      <c r="F143" s="323"/>
+      <c r="G143" s="323"/>
+      <c r="H143" s="323"/>
+      <c r="I143" s="323"/>
+      <c r="J143" s="323"/>
+      <c r="K143" s="323"/>
+      <c r="L143" s="323"/>
+      <c r="M143" s="323"/>
+      <c r="N143" s="323"/>
+      <c r="O143" s="323"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C144" s="323"/>
+      <c r="D144" s="323"/>
+      <c r="E144" s="323"/>
+      <c r="F144" s="323"/>
+      <c r="G144" s="323"/>
+      <c r="H144" s="323"/>
+      <c r="I144" s="323"/>
+      <c r="J144" s="323"/>
+      <c r="K144" s="323"/>
+      <c r="L144" s="323"/>
+      <c r="M144" s="323"/>
+      <c r="N144" s="323"/>
+      <c r="O144" s="323"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C145" s="323"/>
+      <c r="D145" s="323"/>
+      <c r="E145" s="323"/>
+      <c r="F145" s="323"/>
+      <c r="G145" s="323"/>
+      <c r="H145" s="323"/>
+      <c r="I145" s="323"/>
+      <c r="J145" s="323"/>
+      <c r="K145" s="323"/>
+      <c r="L145" s="323"/>
+      <c r="M145" s="323"/>
+      <c r="N145" s="323"/>
+      <c r="O145" s="323"/>
+    </row>
+    <row r="146" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C146" s="323"/>
+      <c r="D146" s="323"/>
+      <c r="E146" s="323"/>
+      <c r="F146" s="323"/>
+      <c r="G146" s="323"/>
+      <c r="H146" s="323"/>
+      <c r="I146" s="323"/>
+      <c r="J146" s="323"/>
+      <c r="K146" s="323"/>
+      <c r="L146" s="323"/>
+      <c r="M146" s="323"/>
+      <c r="N146" s="323"/>
+      <c r="O146" s="323"/>
+    </row>
+    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
       <c r="E147" s="49"/>
@@ -12859,7 +12828,7 @@
       <c r="N147" s="49"/>
       <c r="O147" s="49"/>
     </row>
-    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
       <c r="E148" s="49"/>
@@ -12874,116 +12843,116 @@
       <c r="N148" s="49"/>
       <c r="O148" s="49"/>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="345" t="s">
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="D149" s="345"/>
-      <c r="E149" s="345"/>
-      <c r="F149" s="345"/>
-      <c r="G149" s="345"/>
-      <c r="H149" s="345"/>
-      <c r="I149" s="345"/>
-      <c r="J149" s="345"/>
-      <c r="K149" s="345"/>
-      <c r="L149" s="345"/>
-      <c r="M149" s="345"/>
-      <c r="N149" s="345"/>
-      <c r="O149" s="345"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="345"/>
-      <c r="D150" s="345"/>
-      <c r="E150" s="345"/>
-      <c r="F150" s="345"/>
-      <c r="G150" s="345"/>
-      <c r="H150" s="345"/>
-      <c r="I150" s="345"/>
-      <c r="J150" s="345"/>
-      <c r="K150" s="345"/>
-      <c r="L150" s="345"/>
-      <c r="M150" s="345"/>
-      <c r="N150" s="345"/>
-      <c r="O150" s="345"/>
-    </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C151" s="345"/>
-      <c r="D151" s="345"/>
-      <c r="E151" s="345"/>
-      <c r="F151" s="345"/>
-      <c r="G151" s="345"/>
-      <c r="H151" s="345"/>
-      <c r="I151" s="345"/>
-      <c r="J151" s="345"/>
-      <c r="K151" s="345"/>
-      <c r="L151" s="345"/>
-      <c r="M151" s="345"/>
-      <c r="N151" s="345"/>
-      <c r="O151" s="345"/>
+      <c r="D149" s="339"/>
+      <c r="E149" s="339"/>
+      <c r="F149" s="339"/>
+      <c r="G149" s="339"/>
+      <c r="H149" s="339"/>
+      <c r="I149" s="339"/>
+      <c r="J149" s="339"/>
+      <c r="K149" s="339"/>
+      <c r="L149" s="339"/>
+      <c r="M149" s="339"/>
+      <c r="N149" s="339"/>
+      <c r="O149" s="339"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="339"/>
+      <c r="D150" s="339"/>
+      <c r="E150" s="339"/>
+      <c r="F150" s="339"/>
+      <c r="G150" s="339"/>
+      <c r="H150" s="339"/>
+      <c r="I150" s="339"/>
+      <c r="J150" s="339"/>
+      <c r="K150" s="339"/>
+      <c r="L150" s="339"/>
+      <c r="M150" s="339"/>
+      <c r="N150" s="339"/>
+      <c r="O150" s="339"/>
+    </row>
+    <row r="151" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C151" s="339"/>
+      <c r="D151" s="339"/>
+      <c r="E151" s="339"/>
+      <c r="F151" s="339"/>
+      <c r="G151" s="339"/>
+      <c r="H151" s="339"/>
+      <c r="I151" s="339"/>
+      <c r="J151" s="339"/>
+      <c r="K151" s="339"/>
+      <c r="L151" s="339"/>
+      <c r="M151" s="339"/>
+      <c r="N151" s="339"/>
+      <c r="O151" s="339"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
         <v>-412320.03031993657</v>
       </c>
     </row>
-    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="345"/>
-      <c r="D152" s="345"/>
-      <c r="E152" s="345"/>
-      <c r="F152" s="345"/>
-      <c r="G152" s="345"/>
-      <c r="H152" s="345"/>
-      <c r="I152" s="345"/>
-      <c r="J152" s="345"/>
-      <c r="K152" s="345"/>
-      <c r="L152" s="345"/>
-      <c r="M152" s="345"/>
-      <c r="N152" s="345"/>
-      <c r="O152" s="345"/>
-    </row>
-    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="345"/>
-      <c r="D153" s="345"/>
-      <c r="E153" s="345"/>
-      <c r="F153" s="345"/>
-      <c r="G153" s="345"/>
-      <c r="H153" s="345"/>
-      <c r="I153" s="345"/>
-      <c r="J153" s="345"/>
-      <c r="K153" s="345"/>
-      <c r="L153" s="345"/>
-      <c r="M153" s="345"/>
-      <c r="N153" s="345"/>
-      <c r="O153" s="345"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="345"/>
-      <c r="D154" s="345"/>
-      <c r="E154" s="345"/>
-      <c r="F154" s="345"/>
-      <c r="G154" s="345"/>
-      <c r="H154" s="345"/>
-      <c r="I154" s="345"/>
-      <c r="J154" s="345"/>
-      <c r="K154" s="345"/>
-      <c r="L154" s="345"/>
-      <c r="M154" s="345"/>
-      <c r="N154" s="345"/>
-      <c r="O154" s="345"/>
-    </row>
-    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="345"/>
-      <c r="D155" s="345"/>
-      <c r="E155" s="345"/>
-      <c r="F155" s="345"/>
-      <c r="G155" s="345"/>
-      <c r="H155" s="345"/>
-      <c r="I155" s="345"/>
-      <c r="J155" s="345"/>
-      <c r="K155" s="345"/>
-      <c r="L155" s="345"/>
-      <c r="M155" s="345"/>
-      <c r="N155" s="345"/>
-      <c r="O155" s="345"/>
+    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="339"/>
+      <c r="D152" s="339"/>
+      <c r="E152" s="339"/>
+      <c r="F152" s="339"/>
+      <c r="G152" s="339"/>
+      <c r="H152" s="339"/>
+      <c r="I152" s="339"/>
+      <c r="J152" s="339"/>
+      <c r="K152" s="339"/>
+      <c r="L152" s="339"/>
+      <c r="M152" s="339"/>
+      <c r="N152" s="339"/>
+      <c r="O152" s="339"/>
+    </row>
+    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="339"/>
+      <c r="D153" s="339"/>
+      <c r="E153" s="339"/>
+      <c r="F153" s="339"/>
+      <c r="G153" s="339"/>
+      <c r="H153" s="339"/>
+      <c r="I153" s="339"/>
+      <c r="J153" s="339"/>
+      <c r="K153" s="339"/>
+      <c r="L153" s="339"/>
+      <c r="M153" s="339"/>
+      <c r="N153" s="339"/>
+      <c r="O153" s="339"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="339"/>
+      <c r="D154" s="339"/>
+      <c r="E154" s="339"/>
+      <c r="F154" s="339"/>
+      <c r="G154" s="339"/>
+      <c r="H154" s="339"/>
+      <c r="I154" s="339"/>
+      <c r="J154" s="339"/>
+      <c r="K154" s="339"/>
+      <c r="L154" s="339"/>
+      <c r="M154" s="339"/>
+      <c r="N154" s="339"/>
+      <c r="O154" s="339"/>
+    </row>
+    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C155" s="339"/>
+      <c r="D155" s="339"/>
+      <c r="E155" s="339"/>
+      <c r="F155" s="339"/>
+      <c r="G155" s="339"/>
+      <c r="H155" s="339"/>
+      <c r="I155" s="339"/>
+      <c r="J155" s="339"/>
+      <c r="K155" s="339"/>
+      <c r="L155" s="339"/>
+      <c r="M155" s="339"/>
+      <c r="N155" s="339"/>
+      <c r="O155" s="339"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -13019,37 +12988,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C1:M26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:M25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K1" s="46"/>
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C2" s="237" t="s">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="263" t="s">
         <v>336</v>
       </c>
-      <c r="D2" s="238">
+      <c r="D2" s="264">
         <v>1</v>
       </c>
-      <c r="E2" s="238"/>
+      <c r="E2" s="264"/>
       <c r="F2" s="170"/>
       <c r="G2" s="170"/>
       <c r="H2" s="170"/>
       <c r="I2" s="170"/>
       <c r="J2" s="171"/>
-      <c r="K2" s="280"/>
-      <c r="L2" s="280"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="46"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C3" s="239" t="s">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C3" s="265" t="s">
         <v>337</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="241">
+      <c r="D3" s="266"/>
+      <c r="E3" s="267">
         <v>0</v>
       </c>
       <c r="F3" s="46"/>
@@ -13059,18 +13028,18 @@
       <c r="H3" s="172"/>
       <c r="I3" s="173"/>
       <c r="J3" s="174"/>
-      <c r="K3" s="292"/>
-      <c r="L3" s="292"/>
-      <c r="M3" s="242"/>
-    </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="239" t="s">
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="M3" s="237"/>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C4" s="265" t="s">
         <v>339</v>
       </c>
-      <c r="D4" s="240" t="s">
+      <c r="D4" s="266" t="s">
         <v>340</v>
       </c>
-      <c r="E4" s="240" t="s">
+      <c r="E4" s="266" t="s">
         <v>341</v>
       </c>
       <c r="F4" s="46"/>
@@ -13078,15 +13047,15 @@
         <v>342</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="I4" s="173"/>
       <c r="J4" s="174"/>
-      <c r="K4" s="292"/>
-      <c r="L4" s="292"/>
-      <c r="M4" s="242"/>
-    </row>
-    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
+      <c r="M4" s="237"/>
+    </row>
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="168" t="s">
         <v>343</v>
       </c>
@@ -13097,93 +13066,92 @@
       <c r="H5" s="46"/>
       <c r="I5" s="46"/>
       <c r="J5" s="175"/>
-      <c r="K5" s="292"/>
-      <c r="L5" s="292"/>
-      <c r="M5" s="242"/>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="374" t="s">
-        <v>375</v>
-      </c>
-      <c r="D6" s="375"/>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
-      <c r="G6" s="375"/>
-      <c r="H6" s="375"/>
-      <c r="I6" s="375"/>
-      <c r="J6" s="376"/>
-      <c r="K6" s="280"/>
-      <c r="L6" s="280"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="M5" s="237"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="368" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="369"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
+      <c r="G6" s="369"/>
+      <c r="H6" s="369"/>
+      <c r="I6" s="369"/>
+      <c r="J6" s="370"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
       <c r="M6" s="46"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="377"/>
-      <c r="D7" s="378"/>
-      <c r="E7" s="378"/>
-      <c r="F7" s="378"/>
-      <c r="G7" s="378"/>
-      <c r="H7" s="378"/>
-      <c r="I7" s="378"/>
-      <c r="J7" s="379"/>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="371"/>
+      <c r="D7" s="372"/>
+      <c r="E7" s="372"/>
+      <c r="F7" s="372"/>
+      <c r="G7" s="372"/>
+      <c r="H7" s="372"/>
+      <c r="I7" s="372"/>
+      <c r="J7" s="373"/>
       <c r="K7" s="46"/>
       <c r="L7" s="46"/>
       <c r="M7" s="46"/>
     </row>
-    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="380"/>
-      <c r="D8" s="381"/>
-      <c r="E8" s="381"/>
-      <c r="F8" s="381"/>
-      <c r="G8" s="381"/>
-      <c r="H8" s="381"/>
-      <c r="I8" s="381"/>
-      <c r="J8" s="382"/>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="374"/>
+      <c r="D8" s="375"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
+      <c r="G8" s="375"/>
+      <c r="H8" s="375"/>
+      <c r="I8" s="375"/>
+      <c r="J8" s="376"/>
       <c r="K8" s="46"/>
       <c r="L8" s="46"/>
       <c r="M8" s="46"/>
     </row>
-    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="268" t="s">
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="401" t="s">
         <v>336</v>
       </c>
-      <c r="D11" s="269">
+      <c r="D11" s="402">
         <v>1</v>
       </c>
-      <c r="E11" s="269"/>
+      <c r="E11" s="402"/>
       <c r="F11" s="170"/>
       <c r="G11" s="170"/>
       <c r="H11" s="170"/>
       <c r="I11" s="170"/>
       <c r="J11" s="171"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="270" t="s">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="403" t="s">
         <v>337</v>
       </c>
-      <c r="D12" s="271"/>
-      <c r="E12" s="272">
+      <c r="D12" s="404"/>
+      <c r="E12" s="405">
         <v>0</v>
       </c>
       <c r="F12" s="46"/>
       <c r="G12" s="46" t="s">
         <v>338</v>
       </c>
-      <c r="H12" s="172"/>
+      <c r="H12" s="172" t="s">
+        <v>428</v>
+      </c>
       <c r="I12" s="173"/>
       <c r="J12" s="174"/>
-      <c r="K12" s="280"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="280"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="270" t="s">
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="403" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="271" t="s">
+      <c r="D13" s="404" t="s">
         <v>340</v>
       </c>
-      <c r="E13" s="271" t="s">
+      <c r="E13" s="404" t="s">
         <v>341</v>
       </c>
       <c r="F13" s="46"/>
@@ -13191,185 +13159,157 @@
         <v>342</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="I13" s="173"/>
       <c r="J13" s="174"/>
-      <c r="K13" s="280"/>
-      <c r="L13" s="280"/>
-      <c r="M13" s="280"/>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="168" t="s">
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="403" t="s">
         <v>343</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
+      <c r="D14" s="404"/>
+      <c r="E14" s="404"/>
       <c r="F14" s="46"/>
       <c r="G14" s="46"/>
       <c r="H14" s="46"/>
       <c r="I14" s="46"/>
       <c r="J14" s="175"/>
-      <c r="K14" s="280"/>
-      <c r="L14" s="280"/>
-      <c r="M14" s="280"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="374" t="s">
-        <v>376</v>
-      </c>
-      <c r="D15" s="375"/>
-      <c r="E15" s="375"/>
-      <c r="F15" s="375"/>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="376"/>
-      <c r="K15" s="280"/>
-      <c r="L15" s="280"/>
-      <c r="M15" s="280"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="377"/>
-      <c r="D16" s="378"/>
-      <c r="E16" s="378"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="379"/>
-      <c r="K16" s="280"/>
-      <c r="L16" s="280"/>
-      <c r="M16" s="280"/>
-    </row>
-    <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="380"/>
-      <c r="D17" s="381"/>
-      <c r="E17" s="381"/>
-      <c r="F17" s="381"/>
-      <c r="G17" s="381"/>
-      <c r="H17" s="381"/>
-      <c r="I17" s="381"/>
-      <c r="J17" s="382"/>
-    </row>
-    <row r="19" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C20" s="273" t="s">
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="368" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" s="369"/>
+      <c r="E15" s="369"/>
+      <c r="F15" s="369"/>
+      <c r="G15" s="369"/>
+      <c r="H15" s="369"/>
+      <c r="I15" s="369"/>
+      <c r="J15" s="370"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="371"/>
+      <c r="D16" s="372"/>
+      <c r="E16" s="372"/>
+      <c r="F16" s="372"/>
+      <c r="G16" s="372"/>
+      <c r="H16" s="372"/>
+      <c r="I16" s="372"/>
+      <c r="J16" s="373"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="374"/>
+      <c r="D17" s="375"/>
+      <c r="E17" s="375"/>
+      <c r="F17" s="375"/>
+      <c r="G17" s="375"/>
+      <c r="H17" s="375"/>
+      <c r="I17" s="375"/>
+      <c r="J17" s="376"/>
+    </row>
+    <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="406" t="s">
         <v>336</v>
       </c>
-      <c r="D20" s="274">
+      <c r="D19" s="407">
         <v>1</v>
       </c>
-      <c r="E20" s="274"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="171"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C21" s="275" t="s">
+      <c r="E19" s="407"/>
+      <c r="F19" s="170"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="171"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="408" t="s">
         <v>337</v>
       </c>
-      <c r="D21" s="276"/>
-      <c r="E21" s="277">
-        <v>0</v>
+      <c r="D20" s="409"/>
+      <c r="E20" s="410">
+        <v>0</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H20" s="172" t="s">
+        <v>428</v>
+      </c>
+      <c r="I20" s="173"/>
+      <c r="J20" s="174"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="408" t="s">
+        <v>339</v>
+      </c>
+      <c r="D21" s="409" t="s">
+        <v>340</v>
+      </c>
+      <c r="E21" s="409" t="s">
+        <v>341</v>
       </c>
       <c r="F21" s="46"/>
       <c r="G21" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="H21" s="172" t="s">
-        <v>378</v>
+        <v>342</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>430</v>
       </c>
       <c r="I21" s="173"/>
       <c r="J21" s="174"/>
-      <c r="K21" s="280"/>
-      <c r="L21" s="280"/>
-      <c r="M21" s="280"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C22" s="275" t="s">
-        <v>339</v>
-      </c>
-      <c r="D22" s="276" t="s">
-        <v>340</v>
-      </c>
-      <c r="E22" s="276" t="s">
-        <v>341</v>
-      </c>
+    </row>
+    <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="408" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="409"/>
+      <c r="E22" s="409"/>
       <c r="F22" s="46"/>
-      <c r="G22" s="46" t="s">
-        <v>342</v>
-      </c>
+      <c r="G22" s="46"/>
       <c r="H22" s="46"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="174"/>
-      <c r="K22" s="280"/>
-      <c r="L22" s="280"/>
-      <c r="M22" s="280"/>
-    </row>
-    <row r="23" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="168" t="s">
-        <v>343</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="280"/>
-      <c r="L23" s="280"/>
-      <c r="M23" s="280"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="374" t="s">
-        <v>379</v>
-      </c>
-      <c r="D24" s="375"/>
-      <c r="E24" s="375"/>
-      <c r="F24" s="375"/>
-      <c r="G24" s="375"/>
-      <c r="H24" s="375"/>
-      <c r="I24" s="375"/>
-      <c r="J24" s="376"/>
-      <c r="K24" s="280"/>
-      <c r="L24" s="280"/>
-      <c r="M24" s="280"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="377"/>
-      <c r="D25" s="378"/>
-      <c r="E25" s="378"/>
-      <c r="F25" s="378"/>
-      <c r="G25" s="378"/>
-      <c r="H25" s="378"/>
-      <c r="I25" s="378"/>
-      <c r="J25" s="379"/>
-      <c r="K25" s="280"/>
-      <c r="L25" s="280"/>
-      <c r="M25" s="280"/>
-    </row>
-    <row r="26" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="380"/>
-      <c r="D26" s="381"/>
-      <c r="E26" s="381"/>
-      <c r="F26" s="381"/>
-      <c r="G26" s="381"/>
-      <c r="H26" s="381"/>
-      <c r="I26" s="381"/>
-      <c r="J26" s="382"/>
-      <c r="K26" s="280"/>
-      <c r="L26" s="280"/>
-      <c r="M26" s="280"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="175"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="368" t="s">
+        <v>431</v>
+      </c>
+      <c r="D23" s="369"/>
+      <c r="E23" s="369"/>
+      <c r="F23" s="369"/>
+      <c r="G23" s="369"/>
+      <c r="H23" s="369"/>
+      <c r="I23" s="369"/>
+      <c r="J23" s="370"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="371"/>
+      <c r="D24" s="372"/>
+      <c r="E24" s="372"/>
+      <c r="F24" s="372"/>
+      <c r="G24" s="372"/>
+      <c r="H24" s="372"/>
+      <c r="I24" s="372"/>
+      <c r="J24" s="373"/>
+    </row>
+    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="374"/>
+      <c r="D25" s="375"/>
+      <c r="E25" s="375"/>
+      <c r="F25" s="375"/>
+      <c r="G25" s="375"/>
+      <c r="H25" s="375"/>
+      <c r="I25" s="375"/>
+      <c r="J25" s="376"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C6:J8"/>
     <mergeCell ref="C15:J17"/>
-    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="C23:J25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13378,84 +13318,84 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="386" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="384" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="386"/>
-      <c r="C1" s="386"/>
-      <c r="D1" s="386"/>
-      <c r="E1" s="386"/>
-      <c r="F1" s="386"/>
-      <c r="G1" s="386"/>
-      <c r="H1" s="386"/>
-      <c r="I1" s="386"/>
-      <c r="J1" s="386"/>
-      <c r="K1" s="386"/>
-      <c r="L1" s="386"/>
-      <c r="M1" s="386"/>
-      <c r="N1" s="386"/>
-      <c r="O1" s="387"/>
+      <c r="B1" s="384"/>
+      <c r="C1" s="384"/>
+      <c r="D1" s="384"/>
+      <c r="E1" s="384"/>
+      <c r="F1" s="384"/>
+      <c r="G1" s="384"/>
+      <c r="H1" s="384"/>
+      <c r="I1" s="384"/>
+      <c r="J1" s="384"/>
+      <c r="K1" s="384"/>
+      <c r="L1" s="384"/>
+      <c r="M1" s="384"/>
+      <c r="N1" s="384"/>
+      <c r="O1" s="385"/>
       <c r="R1" s="31"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="388"/>
-      <c r="B2" s="388"/>
-      <c r="C2" s="388"/>
-      <c r="D2" s="388"/>
-      <c r="E2" s="388"/>
-      <c r="F2" s="388"/>
-      <c r="G2" s="388"/>
-      <c r="H2" s="388"/>
-      <c r="I2" s="388"/>
-      <c r="J2" s="388"/>
-      <c r="K2" s="388"/>
-      <c r="L2" s="388"/>
-      <c r="M2" s="388"/>
-      <c r="N2" s="388"/>
-      <c r="O2" s="389"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="386"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
+      <c r="G2" s="386"/>
+      <c r="H2" s="386"/>
+      <c r="I2" s="386"/>
+      <c r="J2" s="386"/>
+      <c r="K2" s="386"/>
+      <c r="L2" s="386"/>
+      <c r="M2" s="386"/>
+      <c r="N2" s="386"/>
+      <c r="O2" s="387"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="383" t="s">
+    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="381" t="s">
         <v>350</v>
       </c>
-      <c r="B3" s="384"/>
-      <c r="C3" s="384"/>
-      <c r="D3" s="384"/>
-      <c r="E3" s="384"/>
-      <c r="F3" s="384"/>
-      <c r="G3" s="384"/>
-      <c r="H3" s="384"/>
-      <c r="I3" s="384"/>
-      <c r="J3" s="384"/>
-      <c r="K3" s="384"/>
-      <c r="L3" s="384"/>
-      <c r="M3" s="384"/>
-      <c r="N3" s="384"/>
-      <c r="O3" s="385"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
+      <c r="L3" s="382"/>
+      <c r="M3" s="382"/>
+      <c r="N3" s="382"/>
+      <c r="O3" s="383"/>
       <c r="P3" s="167"/>
       <c r="Q3" s="167"/>
       <c r="R3" s="167"/>
@@ -13469,89 +13409,89 @@
       <c r="Z3" s="167"/>
       <c r="AA3" s="167"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="338" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="332" t="s">
         <v>294</v>
       </c>
-      <c r="B4" s="338" t="s">
+      <c r="B4" s="332" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="338" t="s">
+      <c r="C4" s="332" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="338" t="s">
+      <c r="D4" s="332" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="335" t="s">
+      <c r="E4" s="329" t="s">
         <v>319</v>
       </c>
-      <c r="F4" s="335" t="s">
+      <c r="F4" s="329" t="s">
         <v>320</v>
       </c>
-      <c r="G4" s="335" t="s">
+      <c r="G4" s="329" t="s">
         <v>256</v>
       </c>
-      <c r="H4" s="335" t="s">
+      <c r="H4" s="329" t="s">
         <v>325</v>
       </c>
-      <c r="I4" s="335" t="s">
+      <c r="I4" s="329" t="s">
         <v>332</v>
       </c>
-      <c r="J4" s="390" t="s">
+      <c r="J4" s="388" t="s">
         <v>321</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="395" t="s">
+      <c r="L4" s="377" t="s">
         <v>329</v>
       </c>
-      <c r="M4" s="335" t="s">
+      <c r="M4" s="329" t="s">
         <v>330</v>
       </c>
-      <c r="N4" s="335" t="s">
+      <c r="N4" s="329" t="s">
         <v>322</v>
       </c>
-      <c r="O4" s="335" t="s">
+      <c r="O4" s="329" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="31"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="339"/>
-      <c r="B5" s="339"/>
-      <c r="C5" s="339"/>
-      <c r="D5" s="339"/>
-      <c r="E5" s="336"/>
-      <c r="F5" s="336"/>
-      <c r="G5" s="336"/>
-      <c r="H5" s="336"/>
-      <c r="I5" s="336"/>
-      <c r="J5" s="391"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="333"/>
+      <c r="B5" s="333"/>
+      <c r="C5" s="333"/>
+      <c r="D5" s="333"/>
+      <c r="E5" s="330"/>
+      <c r="F5" s="330"/>
+      <c r="G5" s="330"/>
+      <c r="H5" s="330"/>
+      <c r="I5" s="330"/>
+      <c r="J5" s="389"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="396"/>
-      <c r="M5" s="336"/>
-      <c r="N5" s="336"/>
-      <c r="O5" s="336"/>
+      <c r="L5" s="378"/>
+      <c r="M5" s="330"/>
+      <c r="N5" s="330"/>
+      <c r="O5" s="330"/>
       <c r="R5" s="31"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="394"/>
-      <c r="B6" s="394"/>
-      <c r="C6" s="394"/>
-      <c r="D6" s="394"/>
-      <c r="E6" s="393"/>
-      <c r="F6" s="393"/>
-      <c r="G6" s="393"/>
-      <c r="H6" s="393"/>
-      <c r="I6" s="393"/>
-      <c r="J6" s="392"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="391"/>
+      <c r="B6" s="391"/>
+      <c r="C6" s="391"/>
+      <c r="D6" s="391"/>
+      <c r="E6" s="380"/>
+      <c r="F6" s="380"/>
+      <c r="G6" s="380"/>
+      <c r="H6" s="380"/>
+      <c r="I6" s="380"/>
+      <c r="J6" s="390"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="397"/>
-      <c r="M6" s="393"/>
-      <c r="N6" s="393"/>
-      <c r="O6" s="393"/>
+      <c r="L6" s="379"/>
+      <c r="M6" s="380"/>
+      <c r="N6" s="380"/>
+      <c r="O6" s="380"/>
       <c r="R6" s="31"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="137" t="s">
         <v>108</v>
       </c>
@@ -13603,10 +13543,10 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="344"/>
-      <c r="S7" s="344"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R7" s="338"/>
+      <c r="S7" s="338"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>301</v>
       </c>
@@ -13659,10 +13599,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="344"/>
-      <c r="S8" s="344"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R8" s="338"/>
+      <c r="S8" s="338"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>109</v>
       </c>
@@ -13718,7 +13658,7 @@
       </c>
       <c r="S9" s="31"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="137" t="s">
         <v>110</v>
       </c>
@@ -13773,7 +13713,7 @@
       </c>
       <c r="S10" s="31"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="141" t="s">
         <v>111</v>
       </c>
@@ -13828,7 +13768,7 @@
       </c>
       <c r="S11" s="31"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="144" t="s">
         <v>39</v>
       </c>
@@ -13884,7 +13824,7 @@
       </c>
       <c r="S12" s="31"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>40</v>
       </c>
@@ -13939,7 +13879,7 @@
       </c>
       <c r="S13" s="31"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>41</v>
       </c>
@@ -13995,7 +13935,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="137" t="s">
         <v>42</v>
       </c>
@@ -14051,7 +13991,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="137" t="s">
         <v>43</v>
       </c>
@@ -14105,7 +14045,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="137" t="s">
         <v>44</v>
       </c>
@@ -14161,7 +14101,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="137" t="s">
         <v>45</v>
       </c>
@@ -14217,7 +14157,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="137" t="s">
         <v>46</v>
       </c>
@@ -14271,7 +14211,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="137" t="s">
         <v>47</v>
       </c>
@@ -14325,7 +14265,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="137" t="s">
         <v>48</v>
       </c>
@@ -14379,7 +14319,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="137" t="s">
         <v>49</v>
       </c>
@@ -14433,7 +14373,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="137" t="s">
         <v>50</v>
       </c>
@@ -14487,7 +14427,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="137" t="s">
         <v>51</v>
       </c>
@@ -14541,7 +14481,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="137" t="s">
         <v>52</v>
       </c>
@@ -14595,7 +14535,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="137" t="s">
         <v>53</v>
       </c>
@@ -14651,7 +14591,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="137" t="s">
         <v>54</v>
       </c>
@@ -14708,7 +14648,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="137" t="s">
         <v>55</v>
       </c>
@@ -14762,7 +14702,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="137" t="s">
         <v>56</v>
       </c>
@@ -14814,7 +14754,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="137" t="s">
         <v>57</v>
       </c>
@@ -14871,7 +14811,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="137" t="s">
         <v>58</v>
       </c>
@@ -14927,7 +14867,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="137" t="s">
         <v>59</v>
       </c>
@@ -15082,7 +15022,7 @@
       <c r="DI32" s="46"/>
       <c r="DJ32" s="46"/>
     </row>
-    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="137" t="s">
         <v>60</v>
       </c>
@@ -15236,7 +15176,7 @@
       <c r="DI33" s="46"/>
       <c r="DJ33" s="46"/>
     </row>
-    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="137" t="s">
         <v>61</v>
       </c>
@@ -15392,7 +15332,7 @@
       <c r="DI34" s="46"/>
       <c r="DJ34" s="46"/>
     </row>
-    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="137" t="s">
         <v>62</v>
       </c>
@@ -15542,7 +15482,7 @@
       <c r="DI35" s="46"/>
       <c r="DJ35" s="46"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="137" t="s">
         <v>63</v>
       </c>
@@ -15598,7 +15538,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="137" t="s">
         <v>64</v>
       </c>
@@ -15652,7 +15592,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="137" t="s">
         <v>65</v>
       </c>
@@ -15714,7 +15654,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="137" t="s">
         <v>66</v>
       </c>
@@ -15770,7 +15710,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="137" t="s">
         <v>67</v>
       </c>
@@ -15824,7 +15764,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="137" t="s">
         <v>68</v>
       </c>
@@ -15878,7 +15818,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="137" t="s">
         <v>69</v>
       </c>
@@ -15934,7 +15874,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="137" t="s">
         <v>70</v>
       </c>
@@ -15991,7 +15931,7 @@
       </c>
       <c r="Q43" s="31"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="137" t="s">
         <v>71</v>
       </c>
@@ -16048,7 +15988,7 @@
       </c>
       <c r="Q44" s="31"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="137" t="s">
         <v>72</v>
       </c>
@@ -16105,7 +16045,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="137" t="s">
         <v>73</v>
       </c>
@@ -16159,7 +16099,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="137" t="s">
         <v>74</v>
       </c>
@@ -16213,7 +16153,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="137" t="s">
         <v>75</v>
       </c>
@@ -16270,7 +16210,7 @@
       </c>
       <c r="R48" s="39"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="137" t="s">
         <v>76</v>
       </c>
@@ -16324,7 +16264,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="137" t="s">
         <v>77</v>
       </c>
@@ -16381,7 +16321,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="137" t="s">
         <v>78</v>
       </c>
@@ -16435,7 +16375,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="137" t="s">
         <v>79</v>
       </c>
@@ -16492,7 +16432,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="137" t="s">
         <v>80</v>
       </c>
@@ -16551,7 +16491,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="137" t="s">
         <v>81</v>
       </c>
@@ -16607,7 +16547,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="137" t="s">
         <v>82</v>
       </c>
@@ -16661,7 +16601,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="137" t="s">
         <v>83</v>
       </c>
@@ -16717,7 +16657,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="137" t="s">
         <v>84</v>
       </c>
@@ -16773,7 +16713,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="137" t="s">
         <v>85</v>
       </c>
@@ -16829,7 +16769,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="137" t="s">
         <v>86</v>
       </c>
@@ -16886,7 +16826,7 @@
       </c>
       <c r="S59" s="125"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="137" t="s">
         <v>87</v>
       </c>
@@ -16943,7 +16883,7 @@
       </c>
       <c r="S60" s="31"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="137" t="s">
         <v>88</v>
       </c>
@@ -16998,7 +16938,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="137" t="s">
         <v>89</v>
       </c>
@@ -17054,7 +16994,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="137" t="s">
         <v>90</v>
       </c>
@@ -17108,7 +17048,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="137" t="s">
         <v>91</v>
       </c>
@@ -17165,7 +17105,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="137" t="s">
         <v>92</v>
       </c>
@@ -17222,7 +17162,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="137" t="s">
         <v>93</v>
       </c>
@@ -17279,7 +17219,7 @@
       </c>
       <c r="Q66" s="46"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="137" t="s">
         <v>94</v>
       </c>
@@ -17335,7 +17275,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="137" t="s">
         <v>95</v>
       </c>
@@ -17381,7 +17321,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="137" t="s">
         <v>96</v>
       </c>
@@ -17436,7 +17376,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="137" t="s">
         <v>97</v>
       </c>
@@ -17492,7 +17432,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="137" t="s">
         <v>98</v>
       </c>
@@ -17548,7 +17488,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="137" t="s">
         <v>99</v>
       </c>
@@ -17604,7 +17544,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="137" t="s">
         <v>100</v>
       </c>
@@ -17659,7 +17599,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="137" t="s">
         <v>101</v>
       </c>
@@ -17715,7 +17655,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="137" t="s">
         <v>102</v>
       </c>
@@ -17769,7 +17709,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="137" t="s">
         <v>103</v>
       </c>
@@ -17825,7 +17765,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="137" t="s">
         <v>104</v>
       </c>
@@ -17881,7 +17821,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="137" t="s">
         <v>105</v>
       </c>
@@ -17937,7 +17877,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="137" t="s">
         <v>106</v>
       </c>
@@ -17993,7 +17933,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="137" t="s">
         <v>107</v>
       </c>
@@ -18049,7 +17989,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="23"/>
       <c r="B81" s="23"/>
       <c r="C81" s="64"/>
@@ -18066,7 +18006,7 @@
       <c r="N81" s="96"/>
       <c r="O81" s="97"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -18107,6 +18047,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
@@ -18122,8 +18064,6 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -18133,38 +18073,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F334087C-F49A-40D2-A732-EFA1FDB50C59}">
   <dimension ref="C2:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="404" t="s">
+    <row r="2" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="398" t="s">
         <v>366</v>
       </c>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="406"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="259" t="s">
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="400"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="254" t="s">
         <v>367</v>
       </c>
-      <c r="D4" s="260" t="s">
+      <c r="D4" s="255" t="s">
         <v>368</v>
       </c>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260" t="s">
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="261"/>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="262" t="str">
+      <c r="H4" s="256"/>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="257" t="str">
         <f>PRORRATEO!C31</f>
         <v>3ºF</v>
       </c>
@@ -18172,49 +18112,49 @@
         <f>PRORRATEO!D31</f>
         <v>Campelo, Mariano</v>
       </c>
-      <c r="G5" s="398">
+      <c r="G5" s="392">
         <f>PRORRATEO!N31</f>
         <v>-7072.88</v>
       </c>
-      <c r="H5" s="399"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="262"/>
-      <c r="H6" s="263"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="262"/>
+      <c r="H5" s="393"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="257"/>
+      <c r="H6" s="258"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="257"/>
       <c r="G7" t="s">
         <v>370</v>
       </c>
-      <c r="H7" s="263"/>
-    </row>
-    <row r="8" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="264"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="400">
-        <v>0</v>
-      </c>
-      <c r="H8" s="401"/>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="259" t="s">
+      <c r="H7" s="258"/>
+    </row>
+    <row r="8" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="259"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="260"/>
+      <c r="G8" s="394">
+        <v>0</v>
+      </c>
+      <c r="H8" s="395"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="254" t="s">
         <v>367</v>
       </c>
-      <c r="D9" s="260" t="s">
+      <c r="D9" s="255" t="s">
         <v>368</v>
       </c>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260" t="s">
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255" t="s">
         <v>369</v>
       </c>
-      <c r="H9" s="261"/>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="262" t="str">
+      <c r="H9" s="256"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="257" t="str">
         <f>PRORRATEO!C37</f>
         <v>4ºF</v>
       </c>
@@ -18222,49 +18162,49 @@
         <f>PRORRATEO!D37</f>
         <v>Campelo, Mariano</v>
       </c>
-      <c r="G10" s="398">
+      <c r="G10" s="392">
         <f>PRORRATEO!N37</f>
         <v>-7071.82</v>
       </c>
-      <c r="H10" s="399"/>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="262"/>
-      <c r="H11" s="263"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="262"/>
+      <c r="H10" s="393"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="257"/>
+      <c r="H11" s="258"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="257"/>
       <c r="G12" t="s">
         <v>371</v>
       </c>
-      <c r="H12" s="263"/>
-    </row>
-    <row r="13" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="264"/>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="400">
-        <v>0</v>
-      </c>
-      <c r="H13" s="401"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="259" t="s">
+      <c r="H12" s="258"/>
+    </row>
+    <row r="13" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="259"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="394">
+        <v>0</v>
+      </c>
+      <c r="H13" s="395"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="254" t="s">
         <v>367</v>
       </c>
-      <c r="D14" s="260" t="s">
+      <c r="D14" s="255" t="s">
         <v>368</v>
       </c>
-      <c r="E14" s="260"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="260" t="s">
+      <c r="E14" s="255"/>
+      <c r="F14" s="255"/>
+      <c r="G14" s="255" t="s">
         <v>369</v>
       </c>
-      <c r="H14" s="261"/>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="262" t="str">
+      <c r="H14" s="256"/>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="257" t="str">
         <f>PRORRATEO!C43</f>
         <v>5ºF</v>
       </c>
@@ -18272,46 +18212,46 @@
         <f>PRORRATEO!D43</f>
         <v>Ayala, Roberto Adrian</v>
       </c>
-      <c r="G15" s="398">
+      <c r="G15" s="392">
         <f>PRORRATEO!N43</f>
         <v>-7072.76</v>
       </c>
-      <c r="H15" s="399"/>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="262"/>
-      <c r="H16" s="263"/>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C17" s="262"/>
+      <c r="H15" s="393"/>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="257"/>
+      <c r="H16" s="258"/>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="257"/>
       <c r="G17" t="s">
         <v>372</v>
       </c>
-      <c r="H17" s="263"/>
-    </row>
-    <row r="18" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="264"/>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="400">
-        <v>0</v>
-      </c>
-      <c r="H18" s="401"/>
-    </row>
-    <row r="19" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="266" t="s">
+      <c r="H17" s="258"/>
+    </row>
+    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="259"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="394">
+        <v>0</v>
+      </c>
+      <c r="H18" s="395"/>
+    </row>
+    <row r="19" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="261" t="s">
         <v>373</v>
       </c>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="402">
+      <c r="D20" s="262"/>
+      <c r="E20" s="262"/>
+      <c r="F20" s="262"/>
+      <c r="G20" s="396">
         <f>G15+G10+G5</f>
         <v>-21217.46</v>
       </c>
-      <c r="H20" s="403"/>
+      <c r="H20" s="397"/>
     </row>
   </sheetData>
   <mergeCells count="8">
